--- a/result/eko_transaction.xlsx
+++ b/result/eko_transaction.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\result\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE99143E-19ED-4768-8145-86A2D77CFCC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D363B73A-E833-4720-BD91-6A496F7E3EFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="38" activeTab="43" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="35" activeTab="37" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Аграрен Университет Пловдив" sheetId="1" r:id="rId1"/>
@@ -6216,10 +6216,10 @@
         <v>18</v>
       </c>
       <c r="H30">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I30">
-        <v>78.430000000000007</v>
+        <v>78.95</v>
       </c>
       <c r="J30">
         <v>1.54</v>
@@ -6456,10 +6456,10 @@
         <v>18</v>
       </c>
       <c r="H36">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="I36">
-        <v>85.06</v>
+        <v>85.61</v>
       </c>
       <c r="J36">
         <v>1.59</v>
@@ -6497,10 +6497,10 @@
         <v>18</v>
       </c>
       <c r="H37">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="I37">
-        <v>31.15</v>
+        <v>31.34</v>
       </c>
       <c r="J37">
         <v>1.71</v>
@@ -6538,10 +6538,10 @@
         <v>18</v>
       </c>
       <c r="H38">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="I38">
-        <v>46.11</v>
+        <v>46.4</v>
       </c>
       <c r="J38">
         <v>1.71</v>
@@ -6579,10 +6579,10 @@
         <v>18</v>
       </c>
       <c r="H39">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="I39">
-        <v>81.599999999999994</v>
+        <v>82.11</v>
       </c>
       <c r="J39">
         <v>1.71</v>
@@ -6702,10 +6702,10 @@
         <v>18</v>
       </c>
       <c r="H42">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="I42">
-        <v>56.13</v>
+        <v>56.47</v>
       </c>
       <c r="J42">
         <v>1.73</v>
@@ -6743,10 +6743,10 @@
         <v>18</v>
       </c>
       <c r="H43">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="I43">
-        <v>56.13</v>
+        <v>56.47</v>
       </c>
       <c r="J43">
         <v>1.73</v>
@@ -6866,10 +6866,10 @@
         <v>18</v>
       </c>
       <c r="H46">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="I46">
-        <v>85.89</v>
+        <v>86.41</v>
       </c>
       <c r="J46">
         <v>1.73</v>
@@ -6907,10 +6907,10 @@
         <v>18</v>
       </c>
       <c r="H47">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="I47">
-        <v>85.89</v>
+        <v>86.41</v>
       </c>
       <c r="J47">
         <v>1.73</v>
@@ -6948,10 +6948,10 @@
         <v>18</v>
       </c>
       <c r="H48">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="I48">
-        <v>85.48</v>
+        <v>86</v>
       </c>
       <c r="J48">
         <v>1.73</v>
@@ -6989,10 +6989,10 @@
         <v>18</v>
       </c>
       <c r="H49">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="I49">
-        <v>85.48</v>
+        <v>86</v>
       </c>
       <c r="J49">
         <v>1.73</v>
@@ -7725,10 +7725,10 @@
         <v>18</v>
       </c>
       <c r="H2">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="I2">
-        <v>56.71</v>
+        <v>57.09</v>
       </c>
       <c r="J2">
         <v>1.51</v>
@@ -7766,10 +7766,10 @@
         <v>18</v>
       </c>
       <c r="H3">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I3">
-        <v>64.459999999999994</v>
+        <v>64.89</v>
       </c>
       <c r="J3">
         <v>1.55</v>
@@ -8186,10 +8186,10 @@
         <v>18</v>
       </c>
       <c r="H8">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="I8">
-        <v>35.72</v>
+        <v>35.979999999999997</v>
       </c>
       <c r="J8">
         <v>1.45</v>
@@ -9109,10 +9109,10 @@
         <v>18</v>
       </c>
       <c r="H10">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I10">
-        <v>620.92999999999995</v>
+        <v>625.29999999999995</v>
       </c>
       <c r="J10">
         <v>1.47</v>
@@ -9150,10 +9150,10 @@
         <v>18</v>
       </c>
       <c r="H11">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="I11">
-        <v>518.41</v>
+        <v>522.01</v>
       </c>
       <c r="J11">
         <v>1.49</v>
@@ -9191,10 +9191,10 @@
         <v>18</v>
       </c>
       <c r="H12">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="I12">
-        <v>82.05</v>
+        <v>82.62</v>
       </c>
       <c r="J12">
         <v>1.49</v>
@@ -9396,10 +9396,10 @@
         <v>18</v>
       </c>
       <c r="H17">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="I17">
-        <v>618.35</v>
+        <v>622.5</v>
       </c>
       <c r="J17">
         <v>1.54</v>
@@ -9437,10 +9437,10 @@
         <v>18</v>
       </c>
       <c r="H18">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="I18">
-        <v>89.97</v>
+        <v>90.56</v>
       </c>
       <c r="J18">
         <v>1.56</v>
@@ -11467,10 +11467,10 @@
         <v>18</v>
       </c>
       <c r="H10">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="I10">
-        <v>95.84</v>
+        <v>96.46</v>
       </c>
       <c r="J10">
         <v>1.59</v>
@@ -11508,10 +11508,10 @@
         <v>18</v>
       </c>
       <c r="H11">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="I11">
-        <v>229.46</v>
+        <v>230.95</v>
       </c>
       <c r="J11">
         <v>1.59</v>
@@ -11549,10 +11549,10 @@
         <v>18</v>
       </c>
       <c r="H12">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="I12">
-        <v>167.07</v>
+        <v>168.16</v>
       </c>
       <c r="J12">
         <v>1.57</v>
@@ -11713,10 +11713,10 @@
         <v>18</v>
       </c>
       <c r="H16">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="I16">
-        <v>256</v>
+        <v>257.60000000000002</v>
       </c>
       <c r="J16">
         <v>1.63</v>
@@ -13975,10 +13975,10 @@
         <v>18</v>
       </c>
       <c r="H15">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I15">
-        <v>822.37</v>
+        <v>827.82</v>
       </c>
       <c r="J15">
         <v>1.55</v>
@@ -14016,10 +14016,10 @@
         <v>18</v>
       </c>
       <c r="H16">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I16">
-        <v>498.79</v>
+        <v>502.09</v>
       </c>
       <c r="J16">
         <v>1.55</v>
@@ -14057,10 +14057,10 @@
         <v>18</v>
       </c>
       <c r="H17">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I17">
-        <v>418.9</v>
+        <v>421.68</v>
       </c>
       <c r="J17">
         <v>1.55</v>
@@ -14576,10 +14576,10 @@
         <v>18</v>
       </c>
       <c r="H8">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I8">
-        <v>28.99</v>
+        <v>29.19</v>
       </c>
       <c r="J8">
         <v>1.47</v>
@@ -14740,10 +14740,10 @@
         <v>18</v>
       </c>
       <c r="H12">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="I12">
-        <v>33.869999999999997</v>
+        <v>34.090000000000003</v>
       </c>
       <c r="J12">
         <v>1.53</v>
@@ -14781,10 +14781,10 @@
         <v>18</v>
       </c>
       <c r="H13">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="I13">
-        <v>69.239999999999995</v>
+        <v>69.69</v>
       </c>
       <c r="J13">
         <v>1.6</v>
@@ -14822,10 +14822,10 @@
         <v>18</v>
       </c>
       <c r="H14">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="I14">
-        <v>46.52</v>
+        <v>46.82</v>
       </c>
       <c r="J14">
         <v>1.59</v>
@@ -14986,10 +14986,10 @@
         <v>18</v>
       </c>
       <c r="H18">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="I18">
-        <v>45.23</v>
+        <v>45.51</v>
       </c>
       <c r="J18">
         <v>1.63</v>
@@ -16423,10 +16423,10 @@
         <v>18</v>
       </c>
       <c r="H5">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="I5">
-        <v>108.9</v>
+        <v>109.64</v>
       </c>
       <c r="J5">
         <v>1.53</v>
@@ -16505,10 +16505,10 @@
         <v>18</v>
       </c>
       <c r="H7">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="I7">
-        <v>108.77</v>
+        <v>109.45</v>
       </c>
       <c r="J7">
         <v>1.63</v>
@@ -16638,10 +16638,10 @@
         <v>18</v>
       </c>
       <c r="H3">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I3">
-        <v>56.86</v>
+        <v>57.24</v>
       </c>
       <c r="J3">
         <v>1.55</v>
@@ -18649,10 +18649,10 @@
         <v>18</v>
       </c>
       <c r="H35">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="I35">
-        <v>68.180000000000007</v>
+        <v>68.67</v>
       </c>
       <c r="J35">
         <v>1.46</v>
@@ -18690,10 +18690,10 @@
         <v>18</v>
       </c>
       <c r="H36">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="I36">
-        <v>73.400000000000006</v>
+        <v>73.92</v>
       </c>
       <c r="J36">
         <v>1.47</v>
@@ -18731,10 +18731,10 @@
         <v>18</v>
       </c>
       <c r="H37">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I37">
-        <v>59.3</v>
+        <v>59.71</v>
       </c>
       <c r="J37">
         <v>1.49</v>
@@ -18807,10 +18807,10 @@
         <v>18</v>
       </c>
       <c r="H39">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I39">
-        <v>56.81</v>
+        <v>57.21</v>
       </c>
       <c r="J39">
         <v>1.48</v>
@@ -18848,10 +18848,10 @@
         <v>18</v>
       </c>
       <c r="H40">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I40">
-        <v>68.099999999999994</v>
+        <v>68.58</v>
       </c>
       <c r="J40">
         <v>1.48</v>
@@ -19568,10 +19568,10 @@
         <v>18</v>
       </c>
       <c r="H58">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="I58">
-        <v>51.8</v>
+        <v>52.15</v>
       </c>
       <c r="J58">
         <v>1.52</v>
@@ -19644,10 +19644,10 @@
         <v>18</v>
       </c>
       <c r="H60">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="I60">
-        <v>62.16</v>
+        <v>62.58</v>
       </c>
       <c r="J60">
         <v>1.52</v>
@@ -19685,10 +19685,10 @@
         <v>18</v>
       </c>
       <c r="H61">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="I61">
-        <v>54.08</v>
+        <v>54.45</v>
       </c>
       <c r="J61">
         <v>1.53</v>
@@ -19761,10 +19761,10 @@
         <v>18</v>
       </c>
       <c r="H63">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="I63">
-        <v>68.66</v>
+        <v>69.12</v>
       </c>
       <c r="J63">
         <v>1.53</v>
@@ -19802,10 +19802,10 @@
         <v>18</v>
       </c>
       <c r="H64">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="I64">
-        <v>61.4</v>
+        <v>61.82</v>
       </c>
       <c r="J64">
         <v>1.52</v>
@@ -19843,10 +19843,10 @@
         <v>18</v>
       </c>
       <c r="H65">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I65">
-        <v>51.79</v>
+        <v>52.13</v>
       </c>
       <c r="J65">
         <v>1.54</v>
@@ -19884,10 +19884,10 @@
         <v>18</v>
       </c>
       <c r="H66">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I66">
-        <v>63.28</v>
+        <v>63.7</v>
       </c>
       <c r="J66">
         <v>1.55</v>
@@ -21055,10 +21055,10 @@
         <v>18</v>
       </c>
       <c r="H95">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="I95">
-        <v>68.8</v>
+        <v>69.23</v>
       </c>
       <c r="J95">
         <v>1.62</v>
@@ -22318,10 +22318,10 @@
         <v>18</v>
       </c>
       <c r="H9">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="I9">
-        <v>58.62</v>
+        <v>59</v>
       </c>
       <c r="J9">
         <v>1.56</v>
@@ -22441,10 +22441,10 @@
         <v>18</v>
       </c>
       <c r="H12">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="I12">
-        <v>51.45</v>
+        <v>51.78</v>
       </c>
       <c r="J12">
         <v>1.57</v>
@@ -22902,10 +22902,10 @@
         <v>18</v>
       </c>
       <c r="H7">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I7">
-        <v>151.97999999999999</v>
+        <v>153.05000000000001</v>
       </c>
       <c r="J7">
         <v>1.47</v>
@@ -26751,10 +26751,10 @@
         <v>18</v>
       </c>
       <c r="H16">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="I16">
-        <v>113.25</v>
+        <v>114.05</v>
       </c>
       <c r="J16">
         <v>1.45</v>
@@ -26792,10 +26792,10 @@
         <v>18</v>
       </c>
       <c r="H17">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="I17">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J17">
         <v>1.45</v>
@@ -26833,10 +26833,10 @@
         <v>18</v>
       </c>
       <c r="H18">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="I18">
-        <v>58.35</v>
+        <v>58.77</v>
       </c>
       <c r="J18">
         <v>1.45</v>
@@ -26874,10 +26874,10 @@
         <v>18</v>
       </c>
       <c r="H19">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I19">
-        <v>53.08</v>
+        <v>53.45</v>
       </c>
       <c r="J19">
         <v>1.48</v>
@@ -26997,10 +26997,10 @@
         <v>18</v>
       </c>
       <c r="H22">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="I22">
-        <v>110.29</v>
+        <v>111.04</v>
       </c>
       <c r="J22">
         <v>1.53</v>
@@ -27038,10 +27038,10 @@
         <v>18</v>
       </c>
       <c r="H23">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="I23">
-        <v>145.72</v>
+        <v>146.71</v>
       </c>
       <c r="J23">
         <v>1.52</v>
@@ -27079,10 +27079,10 @@
         <v>18</v>
       </c>
       <c r="H24">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I24">
-        <v>86.93</v>
+        <v>87.5</v>
       </c>
       <c r="J24">
         <v>1.55</v>
@@ -27776,10 +27776,10 @@
         <v>18</v>
       </c>
       <c r="H41">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="I41">
-        <v>34.49</v>
+        <v>34.71</v>
       </c>
       <c r="J41">
         <v>1.63</v>
@@ -27817,10 +27817,10 @@
         <v>18</v>
       </c>
       <c r="H42">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="I42">
-        <v>102.68</v>
+        <v>103.32</v>
       </c>
       <c r="J42">
         <v>1.63</v>
@@ -28872,10 +28872,10 @@
         <v>18</v>
       </c>
       <c r="H7">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I7">
-        <v>71.510000000000005</v>
+        <v>72.010000000000005</v>
       </c>
       <c r="J7">
         <v>1.48</v>
@@ -29549,10 +29549,10 @@
         <v>18</v>
       </c>
       <c r="H9">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="I9">
-        <v>52.61</v>
+        <v>52.99</v>
       </c>
       <c r="J9">
         <v>1.46</v>
@@ -29625,10 +29625,10 @@
         <v>18</v>
       </c>
       <c r="H11">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I11">
-        <v>59.12</v>
+        <v>59.53</v>
       </c>
       <c r="J11">
         <v>1.49</v>
@@ -29806,10 +29806,10 @@
         <v>18</v>
       </c>
       <c r="H16">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="I16">
-        <v>58.54</v>
+        <v>58.92</v>
       </c>
       <c r="J16">
         <v>1.6</v>
@@ -30318,6 +30318,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2500-000000000000}">
   <dimension ref="A1:M111"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -32023,10 +32026,10 @@
         <v>18</v>
       </c>
       <c r="H42">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="I42">
-        <v>245.35</v>
+        <v>247.1</v>
       </c>
       <c r="J42">
         <v>1.49</v>
@@ -32105,10 +32108,10 @@
         <v>18</v>
       </c>
       <c r="H44">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="I44">
-        <v>78.27</v>
+        <v>78.83</v>
       </c>
       <c r="J44">
         <v>1.45</v>
@@ -32187,10 +32190,10 @@
         <v>18</v>
       </c>
       <c r="H46">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I46">
-        <v>66.739999999999995</v>
+        <v>67.209999999999994</v>
       </c>
       <c r="J46">
         <v>1.49</v>
@@ -32228,10 +32231,10 @@
         <v>18</v>
       </c>
       <c r="H47">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I47">
-        <v>339.38</v>
+        <v>341.77</v>
       </c>
       <c r="J47">
         <v>1.49</v>
@@ -32269,10 +32272,10 @@
         <v>18</v>
       </c>
       <c r="H48">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I48">
-        <v>320.02</v>
+        <v>322.27999999999997</v>
       </c>
       <c r="J48">
         <v>1.49</v>
@@ -32761,10 +32764,10 @@
         <v>18</v>
       </c>
       <c r="H60">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="I60">
-        <v>458.85</v>
+        <v>461.95</v>
       </c>
       <c r="J60">
         <v>1.54</v>
@@ -32843,10 +32846,10 @@
         <v>18</v>
       </c>
       <c r="H62">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="I62">
-        <v>321.16000000000003</v>
+        <v>323.33</v>
       </c>
       <c r="J62">
         <v>1.54</v>
@@ -32884,10 +32887,10 @@
         <v>18</v>
       </c>
       <c r="H63">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="I63">
-        <v>338.3</v>
+        <v>340.59</v>
       </c>
       <c r="J63">
         <v>1.53</v>
@@ -32925,10 +32928,10 @@
         <v>18</v>
       </c>
       <c r="H64">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="I64">
-        <v>82.24</v>
+        <v>82.8</v>
       </c>
       <c r="J64">
         <v>1.53</v>
@@ -32966,10 +32969,10 @@
         <v>18</v>
       </c>
       <c r="H65">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="I65">
-        <v>68.42</v>
+        <v>68.89</v>
       </c>
       <c r="J65">
         <v>1.51</v>
@@ -33007,10 +33010,10 @@
         <v>18</v>
       </c>
       <c r="H66">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I66">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J66">
         <v>1.56</v>
@@ -33335,10 +33338,10 @@
         <v>18</v>
       </c>
       <c r="H74">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="I74">
-        <v>101.64</v>
+        <v>102.3</v>
       </c>
       <c r="J74">
         <v>1.59</v>
@@ -33376,10 +33379,10 @@
         <v>18</v>
       </c>
       <c r="H75">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="I75">
-        <v>237.66</v>
+        <v>239.2</v>
       </c>
       <c r="J75">
         <v>1.58</v>
@@ -34442,10 +34445,10 @@
         <v>18</v>
       </c>
       <c r="H101">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="I101">
-        <v>283.07</v>
+        <v>284.83999999999997</v>
       </c>
       <c r="J101">
         <v>1.63</v>
@@ -34483,10 +34486,10 @@
         <v>18</v>
       </c>
       <c r="H102">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="I102">
-        <v>295.87</v>
+        <v>297.72000000000003</v>
       </c>
       <c r="J102">
         <v>1.63</v>
@@ -34524,10 +34527,10 @@
         <v>18</v>
       </c>
       <c r="H103">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="I103">
-        <v>355.2</v>
+        <v>357.42</v>
       </c>
       <c r="J103">
         <v>1.63</v>
@@ -35160,10 +35163,10 @@
         <v>18</v>
       </c>
       <c r="H8">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="I8">
-        <v>72.69</v>
+        <v>73.2</v>
       </c>
       <c r="J8">
         <v>1.47</v>
@@ -35201,10 +35204,10 @@
         <v>18</v>
       </c>
       <c r="H9">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I9">
-        <v>84.96</v>
+        <v>85.56</v>
       </c>
       <c r="J9">
         <v>1.49</v>
@@ -35242,10 +35245,10 @@
         <v>18</v>
       </c>
       <c r="H10">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="I10">
-        <v>84.64</v>
+        <v>85.21</v>
       </c>
       <c r="J10">
         <v>1.53</v>
@@ -37183,10 +37186,10 @@
         <v>18</v>
       </c>
       <c r="H37">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="I37">
-        <v>57.24</v>
+        <v>57.65</v>
       </c>
       <c r="J37">
         <v>1.47</v>
@@ -37224,10 +37227,10 @@
         <v>18</v>
       </c>
       <c r="H38">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="I38">
-        <v>61.71</v>
+        <v>62.15</v>
       </c>
       <c r="J38">
         <v>1.47</v>
@@ -37265,10 +37268,10 @@
         <v>18</v>
       </c>
       <c r="H39">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="I39">
-        <v>73.02</v>
+        <v>73.540000000000006</v>
       </c>
       <c r="J39">
         <v>1.47</v>
@@ -37306,10 +37309,10 @@
         <v>18</v>
       </c>
       <c r="H40">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="I40">
-        <v>93.37</v>
+        <v>94.03</v>
       </c>
       <c r="J40">
         <v>1.47</v>
@@ -37382,10 +37385,10 @@
         <v>18</v>
       </c>
       <c r="H42">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I42">
-        <v>70.3</v>
+        <v>70.8</v>
       </c>
       <c r="J42">
         <v>1.48</v>
@@ -37423,10 +37426,10 @@
         <v>18</v>
       </c>
       <c r="H43">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I43">
-        <v>99.02</v>
+        <v>99.71</v>
       </c>
       <c r="J43">
         <v>1.48</v>
@@ -37464,10 +37467,10 @@
         <v>18</v>
       </c>
       <c r="H44">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I44">
-        <v>70.8</v>
+        <v>71.3</v>
       </c>
       <c r="J44">
         <v>1.49</v>
@@ -37505,10 +37508,10 @@
         <v>18</v>
       </c>
       <c r="H45">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I45">
-        <v>95.1</v>
+        <v>95.77</v>
       </c>
       <c r="J45">
         <v>1.46</v>
@@ -37546,10 +37549,10 @@
         <v>18</v>
       </c>
       <c r="H46">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I46">
-        <v>97.19</v>
+        <v>97.88</v>
       </c>
       <c r="J46">
         <v>1.48</v>
@@ -37587,10 +37590,10 @@
         <v>18</v>
       </c>
       <c r="H47">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I47">
-        <v>87.04</v>
+        <v>87.66</v>
       </c>
       <c r="J47">
         <v>1.47</v>
@@ -37628,10 +37631,10 @@
         <v>18</v>
       </c>
       <c r="H48">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I48">
-        <v>25.46</v>
+        <v>25.64</v>
       </c>
       <c r="J48">
         <v>1.47</v>
@@ -37669,10 +37672,10 @@
         <v>18</v>
       </c>
       <c r="H49">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I49">
-        <v>84.84</v>
+        <v>85.44</v>
       </c>
       <c r="J49">
         <v>1.47</v>
@@ -38026,10 +38029,10 @@
         <v>18</v>
       </c>
       <c r="H58">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="I58">
-        <v>96.7</v>
+        <v>97.35</v>
       </c>
       <c r="J58">
         <v>1.54</v>
@@ -38067,10 +38070,10 @@
         <v>18</v>
       </c>
       <c r="H59">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="I59">
-        <v>99.68</v>
+        <v>100.36</v>
       </c>
       <c r="J59">
         <v>1.53</v>
@@ -38108,10 +38111,10 @@
         <v>18</v>
       </c>
       <c r="H60">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="I60">
-        <v>107.21</v>
+        <v>107.94</v>
       </c>
       <c r="J60">
         <v>1.56</v>
@@ -38149,10 +38152,10 @@
         <v>18</v>
       </c>
       <c r="H61">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I61">
-        <v>78.52</v>
+        <v>79.040000000000006</v>
       </c>
       <c r="J61">
         <v>1.56</v>
@@ -38190,10 +38193,10 @@
         <v>18</v>
       </c>
       <c r="H62">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I62">
-        <v>91.55</v>
+        <v>92.15</v>
       </c>
       <c r="J62">
         <v>1.56</v>
@@ -38231,10 +38234,10 @@
         <v>18</v>
       </c>
       <c r="H63">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I63">
-        <v>106.63</v>
+        <v>107.34</v>
       </c>
       <c r="J63">
         <v>1.55</v>
@@ -39168,10 +39171,10 @@
         <v>18</v>
       </c>
       <c r="H86">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="I86">
-        <v>96.38</v>
+        <v>96.98</v>
       </c>
       <c r="J86">
         <v>1.63</v>
@@ -39209,10 +39212,10 @@
         <v>18</v>
       </c>
       <c r="H87">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="I87">
-        <v>83.86</v>
+        <v>84.38</v>
       </c>
       <c r="J87">
         <v>1.63</v>
@@ -39250,10 +39253,10 @@
         <v>18</v>
       </c>
       <c r="H88">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="I88">
-        <v>126.12</v>
+        <v>126.9</v>
       </c>
       <c r="J88">
         <v>1.63</v>
@@ -40197,10 +40200,10 @@
         <v>18</v>
       </c>
       <c r="H8">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="I8">
-        <v>37.19</v>
+        <v>37.43</v>
       </c>
       <c r="J8">
         <v>1.59</v>
@@ -42128,10 +42131,10 @@
         <v>18</v>
       </c>
       <c r="H42">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="I42">
-        <v>88.33</v>
+        <v>88.96</v>
       </c>
       <c r="J42">
         <v>1.47</v>
@@ -42169,10 +42172,10 @@
         <v>18</v>
       </c>
       <c r="H43">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="I43">
-        <v>65.69</v>
+        <v>66.150000000000006</v>
       </c>
       <c r="J43">
         <v>1.47</v>
@@ -42210,10 +42213,10 @@
         <v>18</v>
       </c>
       <c r="H44">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="I44">
-        <v>45.39</v>
+        <v>45.72</v>
       </c>
       <c r="J44">
         <v>1.47</v>
@@ -42251,10 +42254,10 @@
         <v>18</v>
       </c>
       <c r="H45">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="I45">
-        <v>83.93</v>
+        <v>84.53</v>
       </c>
       <c r="J45">
         <v>1.46</v>
@@ -42292,10 +42295,10 @@
         <v>18</v>
       </c>
       <c r="H46">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="I46">
-        <v>55.69</v>
+        <v>56.09</v>
       </c>
       <c r="J46">
         <v>1.49</v>
@@ -42333,10 +42336,10 @@
         <v>18</v>
       </c>
       <c r="H47">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="I47">
-        <v>63.28</v>
+        <v>63.73</v>
       </c>
       <c r="J47">
         <v>1.47</v>
@@ -42374,10 +42377,10 @@
         <v>18</v>
       </c>
       <c r="H48">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I48">
-        <v>82.07</v>
+        <v>82.65</v>
       </c>
       <c r="J48">
         <v>1.48</v>
@@ -42415,10 +42418,10 @@
         <v>18</v>
       </c>
       <c r="H49">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I49">
-        <v>47.18</v>
+        <v>47.52</v>
       </c>
       <c r="J49">
         <v>1.49</v>
@@ -42456,10 +42459,10 @@
         <v>18</v>
       </c>
       <c r="H50">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I50">
-        <v>74.13</v>
+        <v>74.650000000000006</v>
       </c>
       <c r="J50">
         <v>1.49</v>
@@ -42497,10 +42500,10 @@
         <v>18</v>
       </c>
       <c r="H51">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I51">
-        <v>125.47</v>
+        <v>126.36</v>
       </c>
       <c r="J51">
         <v>1.49</v>
@@ -42538,10 +42541,10 @@
         <v>18</v>
       </c>
       <c r="H52">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I52">
-        <v>41.5</v>
+        <v>41.8</v>
       </c>
       <c r="J52">
         <v>1.49</v>
@@ -43071,10 +43074,10 @@
         <v>18</v>
       </c>
       <c r="H65">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="I65">
-        <v>99.22</v>
+        <v>99.89</v>
       </c>
       <c r="J65">
         <v>1.54</v>
@@ -43112,10 +43115,10 @@
         <v>18</v>
       </c>
       <c r="H66">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="I66">
-        <v>51.71</v>
+        <v>52.04</v>
       </c>
       <c r="J66">
         <v>1.8</v>
@@ -43153,10 +43156,10 @@
         <v>18</v>
       </c>
       <c r="H67">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I67">
-        <v>45.87</v>
+        <v>46.17</v>
       </c>
       <c r="J67">
         <v>1.56</v>
@@ -43235,10 +43238,10 @@
         <v>18</v>
       </c>
       <c r="H69">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I69">
-        <v>84.32</v>
+        <v>84.88</v>
       </c>
       <c r="J69">
         <v>1.56</v>
@@ -43276,10 +43279,10 @@
         <v>18</v>
       </c>
       <c r="H70">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I70">
-        <v>80.89</v>
+        <v>81.430000000000007</v>
       </c>
       <c r="J70">
         <v>1.54</v>
@@ -43358,10 +43361,10 @@
         <v>18</v>
       </c>
       <c r="H72">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I72">
-        <v>147.69999999999999</v>
+        <v>148.68</v>
       </c>
       <c r="J72">
         <v>1.53</v>
@@ -43434,10 +43437,10 @@
         <v>18</v>
       </c>
       <c r="H74">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I74">
-        <v>47.11</v>
+        <v>47.42</v>
       </c>
       <c r="J74">
         <v>1.56</v>
@@ -43475,10 +43478,10 @@
         <v>18</v>
       </c>
       <c r="H75">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I75">
-        <v>51.69</v>
+        <v>52.03</v>
       </c>
       <c r="J75">
         <v>1.56</v>
@@ -43762,10 +43765,10 @@
         <v>18</v>
       </c>
       <c r="H82">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="I82">
-        <v>131.69</v>
+        <v>132.49</v>
       </c>
       <c r="J82">
         <v>1.86</v>
@@ -43803,10 +43806,10 @@
         <v>18</v>
       </c>
       <c r="H83">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="I83">
-        <v>131.69</v>
+        <v>132.49</v>
       </c>
       <c r="J83">
         <v>1.86</v>
@@ -43844,10 +43847,10 @@
         <v>18</v>
       </c>
       <c r="H84">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="I84">
-        <v>54.53</v>
+        <v>54.86</v>
       </c>
       <c r="J84">
         <v>1.86</v>
@@ -43885,10 +43888,10 @@
         <v>18</v>
       </c>
       <c r="H85">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="I85">
-        <v>54.53</v>
+        <v>54.86</v>
       </c>
       <c r="J85">
         <v>1.86</v>
@@ -44254,10 +44257,10 @@
         <v>18</v>
       </c>
       <c r="H94">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="I94">
-        <v>73.39</v>
+        <v>73.83</v>
       </c>
       <c r="J94">
         <v>1.86</v>
@@ -44295,10 +44298,10 @@
         <v>18</v>
       </c>
       <c r="H95">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="I95">
-        <v>73.39</v>
+        <v>73.83</v>
       </c>
       <c r="J95">
         <v>1.86</v>
@@ -44945,10 +44948,10 @@
         <v>18</v>
       </c>
       <c r="H111">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="I111">
-        <v>59.99</v>
+        <v>60.36</v>
       </c>
       <c r="J111">
         <v>1.63</v>
@@ -45597,13 +45600,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2B00-000000000000}">
   <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.85546875" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -46223,10 +46219,10 @@
         <v>18</v>
       </c>
       <c r="H10">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="I10">
-        <v>700</v>
+        <v>705</v>
       </c>
       <c r="J10">
         <v>1.49</v>
@@ -46264,10 +46260,10 @@
         <v>18</v>
       </c>
       <c r="H11">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="I11">
-        <v>1260</v>
+        <v>1269</v>
       </c>
       <c r="J11">
         <v>1.47</v>
@@ -46305,10 +46301,10 @@
         <v>18</v>
       </c>
       <c r="H12">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="I12">
-        <v>70</v>
+        <v>70.5</v>
       </c>
       <c r="J12">
         <v>1.49</v>
@@ -46346,10 +46342,10 @@
         <v>18</v>
       </c>
       <c r="H13">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I13">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="J13">
         <v>1.49</v>
@@ -46387,10 +46383,10 @@
         <v>18</v>
       </c>
       <c r="H14">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I14">
-        <v>63.83</v>
+        <v>64.28</v>
       </c>
       <c r="J14">
         <v>1.49</v>
@@ -49560,10 +49556,10 @@
         <v>18</v>
       </c>
       <c r="H8">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="I8">
-        <v>19.649999999999999</v>
+        <v>19.77</v>
       </c>
       <c r="J8">
         <v>1.63</v>
@@ -50249,10 +50245,10 @@
         <v>18</v>
       </c>
       <c r="H17">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="I17">
-        <v>74.34</v>
+        <v>74.88</v>
       </c>
       <c r="J17">
         <v>1.45</v>
@@ -50290,10 +50286,10 @@
         <v>18</v>
       </c>
       <c r="H18">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="I18">
-        <v>29.67</v>
+        <v>29.88</v>
       </c>
       <c r="J18">
         <v>1.47</v>
@@ -50331,10 +50327,10 @@
         <v>18</v>
       </c>
       <c r="H19">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="I19">
-        <v>79.84</v>
+        <v>80.41</v>
       </c>
       <c r="J19">
         <v>1.44</v>
@@ -50372,10 +50368,10 @@
         <v>18</v>
       </c>
       <c r="H20">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I20">
-        <v>59.11</v>
+        <v>59.53</v>
       </c>
       <c r="J20">
         <v>1.48</v>
@@ -50413,10 +50409,10 @@
         <v>18</v>
       </c>
       <c r="H21">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I21">
-        <v>90.39</v>
+        <v>91.02</v>
       </c>
       <c r="J21">
         <v>1.47</v>
@@ -50571,10 +50567,10 @@
         <v>18</v>
       </c>
       <c r="H25">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="I25">
-        <v>22.51</v>
+        <v>22.66</v>
       </c>
       <c r="J25">
         <v>1.53</v>
@@ -50612,10 +50608,10 @@
         <v>18</v>
       </c>
       <c r="H26">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="I26">
-        <v>84.52</v>
+        <v>85.1</v>
       </c>
       <c r="J26">
         <v>1.53</v>
@@ -50653,10 +50649,10 @@
         <v>18</v>
       </c>
       <c r="H27">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="I27">
-        <v>47.1</v>
+        <v>47.41</v>
       </c>
       <c r="J27">
         <v>1.52</v>
@@ -50694,10 +50690,10 @@
         <v>18</v>
       </c>
       <c r="H28">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I28">
-        <v>114.76</v>
+        <v>115.52</v>
       </c>
       <c r="J28">
         <v>1.56</v>
@@ -50735,10 +50731,10 @@
         <v>18</v>
       </c>
       <c r="H29">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I29">
-        <v>123.54</v>
+        <v>124.36</v>
       </c>
       <c r="J29">
         <v>1.53</v>
@@ -50776,10 +50772,10 @@
         <v>18</v>
       </c>
       <c r="H30">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I30">
-        <v>75.5</v>
+        <v>76</v>
       </c>
       <c r="J30">
         <v>1.56</v>
@@ -51947,10 +51943,10 @@
         <v>18</v>
       </c>
       <c r="H59">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="I59">
-        <v>26.06</v>
+        <v>26.22</v>
       </c>
       <c r="J59">
         <v>1.63</v>

--- a/result/eko_transaction.xlsx
+++ b/result/eko_transaction.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sveto\OneDrive\Desktop\eko_inv\result\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E31E0FE8-697D-4ABE-B266-91EF9E93C66A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D634CFB6-E7D7-4698-8887-BBA96FB09843}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="37" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="30" activeTab="32" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="АГРАРЕН УНИВЕРСИТЕТ - ПЛОВДИВ" sheetId="1" r:id="rId1"/>
@@ -3017,6 +3017,12 @@
     <t>07:33:00</t>
   </si>
   <si>
+    <t>78970153027720209</t>
+  </si>
+  <si>
+    <t>00:41:00</t>
+  </si>
+  <si>
     <t>12:04:00</t>
   </si>
   <si>
@@ -3993,12 +3999,6 @@
   </si>
   <si>
     <t>1125 Гоце Делчев</t>
-  </si>
-  <si>
-    <t>78970153027720209</t>
-  </si>
-  <si>
-    <t>00:41:00</t>
   </si>
   <si>
     <t>1110 Петрич вход</t>
@@ -10821,6 +10821,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:M22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="22.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -21625,9 +21628,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="14.28515625" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -25024,8 +25024,11 @@
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2000-000000000000}">
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="18.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -26221,37 +26224,37 @@
         <v>49</v>
       </c>
       <c r="B30" t="s">
-        <v>151</v>
+        <v>375</v>
       </c>
       <c r="C30" t="s">
-        <v>960</v>
+        <v>411</v>
       </c>
       <c r="D30" t="s">
-        <v>961</v>
+        <v>984</v>
       </c>
       <c r="E30" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="F30">
-        <v>97.143000000000001</v>
+        <v>26.431999999999899</v>
       </c>
       <c r="G30" t="s">
         <v>18</v>
       </c>
       <c r="H30">
-        <v>1.57</v>
+        <v>1.39</v>
       </c>
       <c r="I30">
-        <v>152.51</v>
+        <v>36.74</v>
       </c>
       <c r="J30">
-        <v>1.61</v>
+        <v>1.46</v>
       </c>
       <c r="K30">
-        <v>156.4</v>
+        <v>38.590000000000003</v>
       </c>
       <c r="L30" t="s">
-        <v>812</v>
+        <v>985</v>
       </c>
       <c r="M30">
         <v>0</v>
@@ -26262,37 +26265,37 @@
         <v>49</v>
       </c>
       <c r="B31" t="s">
-        <v>97</v>
+        <v>151</v>
       </c>
       <c r="C31" t="s">
-        <v>946</v>
+        <v>960</v>
       </c>
       <c r="D31" t="s">
-        <v>947</v>
+        <v>961</v>
       </c>
       <c r="E31" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="F31">
-        <v>19.651</v>
+        <v>97.143000000000001</v>
       </c>
       <c r="G31" t="s">
         <v>18</v>
       </c>
       <c r="H31">
-        <v>1.39</v>
+        <v>1.57</v>
       </c>
       <c r="I31">
-        <v>27.31</v>
+        <v>152.51</v>
       </c>
       <c r="J31">
-        <v>1.46</v>
+        <v>1.61</v>
       </c>
       <c r="K31">
-        <v>28.69</v>
+        <v>156.4</v>
       </c>
       <c r="L31" t="s">
-        <v>374</v>
+        <v>812</v>
       </c>
       <c r="M31">
         <v>0</v>
@@ -26300,40 +26303,40 @@
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="B32" t="s">
-        <v>151</v>
+        <v>97</v>
       </c>
       <c r="C32" t="s">
-        <v>960</v>
+        <v>946</v>
       </c>
       <c r="D32" t="s">
-        <v>961</v>
+        <v>947</v>
       </c>
       <c r="E32" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="F32">
-        <v>96.067999999999898</v>
+        <v>19.651</v>
       </c>
       <c r="G32" t="s">
         <v>18</v>
       </c>
       <c r="H32">
-        <v>1.6</v>
+        <v>1.39</v>
       </c>
       <c r="I32">
-        <v>153.71</v>
+        <v>27.31</v>
       </c>
       <c r="J32">
-        <v>1.61</v>
+        <v>1.46</v>
       </c>
       <c r="K32">
-        <v>154.66999999999999</v>
+        <v>28.69</v>
       </c>
       <c r="L32" t="s">
-        <v>812</v>
+        <v>374</v>
       </c>
       <c r="M32">
         <v>0</v>
@@ -26344,19 +26347,19 @@
         <v>69</v>
       </c>
       <c r="B33" t="s">
-        <v>97</v>
+        <v>151</v>
       </c>
       <c r="C33" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="D33" t="s">
-        <v>954</v>
+        <v>961</v>
       </c>
       <c r="E33" t="s">
         <v>17</v>
       </c>
       <c r="F33">
-        <v>92.298000000000002</v>
+        <v>96.067999999999898</v>
       </c>
       <c r="G33" t="s">
         <v>18</v>
@@ -26365,16 +26368,16 @@
         <v>1.6</v>
       </c>
       <c r="I33">
-        <v>147.68</v>
+        <v>153.71</v>
       </c>
       <c r="J33">
         <v>1.61</v>
       </c>
       <c r="K33">
-        <v>148.6</v>
+        <v>154.66999999999999</v>
       </c>
       <c r="L33" t="s">
-        <v>984</v>
+        <v>812</v>
       </c>
       <c r="M33">
         <v>0</v>
@@ -26382,40 +26385,40 @@
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="B34" t="s">
-        <v>380</v>
+        <v>97</v>
       </c>
       <c r="C34" t="s">
-        <v>946</v>
+        <v>953</v>
       </c>
       <c r="D34" t="s">
-        <v>947</v>
+        <v>954</v>
       </c>
       <c r="E34" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="F34">
-        <v>29.748000000000001</v>
+        <v>92.298000000000002</v>
       </c>
       <c r="G34" t="s">
         <v>18</v>
       </c>
       <c r="H34">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="I34">
-        <v>41.65</v>
+        <v>147.68</v>
       </c>
       <c r="J34">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="K34">
-        <v>43.73</v>
+        <v>148.6</v>
       </c>
       <c r="L34" t="s">
-        <v>969</v>
+        <v>986</v>
       </c>
       <c r="M34">
         <v>0</v>
@@ -26429,34 +26432,34 @@
         <v>380</v>
       </c>
       <c r="C35" t="s">
-        <v>985</v>
+        <v>946</v>
       </c>
       <c r="D35" t="s">
-        <v>986</v>
+        <v>947</v>
       </c>
       <c r="E35" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="F35">
-        <v>56.2899999999999</v>
+        <v>29.748000000000001</v>
       </c>
       <c r="G35" t="s">
         <v>18</v>
       </c>
       <c r="H35">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="I35">
-        <v>90.06</v>
+        <v>41.65</v>
       </c>
       <c r="J35">
-        <v>1.62</v>
+        <v>1.47</v>
       </c>
       <c r="K35">
-        <v>91.19</v>
+        <v>43.73</v>
       </c>
       <c r="L35" t="s">
-        <v>987</v>
+        <v>969</v>
       </c>
       <c r="M35">
         <v>0</v>
@@ -26464,40 +26467,40 @@
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>135</v>
+        <v>53</v>
       </c>
       <c r="B36" t="s">
         <v>380</v>
       </c>
       <c r="C36" t="s">
-        <v>946</v>
+        <v>987</v>
       </c>
       <c r="D36" t="s">
-        <v>947</v>
+        <v>988</v>
       </c>
       <c r="E36" t="s">
         <v>17</v>
       </c>
       <c r="F36">
-        <v>21.558</v>
+        <v>56.2899999999999</v>
       </c>
       <c r="G36" t="s">
         <v>18</v>
       </c>
       <c r="H36">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="I36">
-        <v>34.71</v>
+        <v>90.06</v>
       </c>
       <c r="J36">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="K36">
-        <v>35.14</v>
+        <v>91.19</v>
       </c>
       <c r="L36" t="s">
-        <v>28</v>
+        <v>989</v>
       </c>
       <c r="M36">
         <v>0</v>
@@ -26508,19 +26511,19 @@
         <v>135</v>
       </c>
       <c r="B37" t="s">
-        <v>97</v>
+        <v>380</v>
       </c>
       <c r="C37" t="s">
-        <v>965</v>
+        <v>946</v>
       </c>
       <c r="D37" t="s">
-        <v>966</v>
+        <v>947</v>
       </c>
       <c r="E37" t="s">
         <v>17</v>
       </c>
       <c r="F37">
-        <v>64.171999999999898</v>
+        <v>21.558</v>
       </c>
       <c r="G37" t="s">
         <v>18</v>
@@ -26529,16 +26532,16 @@
         <v>1.61</v>
       </c>
       <c r="I37">
-        <v>103.32</v>
+        <v>34.71</v>
       </c>
       <c r="J37">
         <v>1.63</v>
       </c>
       <c r="K37">
-        <v>104.6</v>
+        <v>35.14</v>
       </c>
       <c r="L37" t="s">
-        <v>246</v>
+        <v>28</v>
       </c>
       <c r="M37">
         <v>0</v>
@@ -26546,40 +26549,40 @@
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>72</v>
+        <v>135</v>
       </c>
       <c r="B38" t="s">
-        <v>151</v>
+        <v>97</v>
       </c>
       <c r="C38" t="s">
-        <v>960</v>
+        <v>965</v>
       </c>
       <c r="D38" t="s">
-        <v>961</v>
+        <v>966</v>
       </c>
       <c r="E38" t="s">
         <v>17</v>
       </c>
       <c r="F38">
-        <v>135.071</v>
+        <v>64.171999999999898</v>
       </c>
       <c r="G38" t="s">
         <v>18</v>
       </c>
       <c r="H38">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="I38">
-        <v>221.52</v>
+        <v>103.32</v>
       </c>
       <c r="J38">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="K38">
-        <v>226.92</v>
+        <v>104.6</v>
       </c>
       <c r="L38" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="M38">
         <v>0</v>
@@ -26590,19 +26593,19 @@
         <v>72</v>
       </c>
       <c r="B39" t="s">
-        <v>97</v>
+        <v>151</v>
       </c>
       <c r="C39" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="D39" t="s">
-        <v>954</v>
+        <v>961</v>
       </c>
       <c r="E39" t="s">
         <v>17</v>
       </c>
       <c r="F39">
-        <v>103.381</v>
+        <v>135.071</v>
       </c>
       <c r="G39" t="s">
         <v>18</v>
@@ -26611,16 +26614,16 @@
         <v>1.64</v>
       </c>
       <c r="I39">
-        <v>169.54</v>
+        <v>221.52</v>
       </c>
       <c r="J39">
         <v>1.68</v>
       </c>
       <c r="K39">
-        <v>173.68</v>
+        <v>226.92</v>
       </c>
       <c r="L39" t="s">
-        <v>984</v>
+        <v>223</v>
       </c>
       <c r="M39">
         <v>0</v>
@@ -26628,40 +26631,40 @@
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="B40" t="s">
-        <v>151</v>
+        <v>97</v>
       </c>
       <c r="C40" t="s">
-        <v>960</v>
+        <v>953</v>
       </c>
       <c r="D40" t="s">
-        <v>961</v>
+        <v>954</v>
       </c>
       <c r="E40" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="F40">
-        <v>19.6419999999999</v>
+        <v>103.381</v>
       </c>
       <c r="G40" t="s">
         <v>18</v>
       </c>
       <c r="H40">
-        <v>1.42</v>
+        <v>1.64</v>
       </c>
       <c r="I40">
-        <v>27.89</v>
+        <v>169.54</v>
       </c>
       <c r="J40">
-        <v>1.48</v>
+        <v>1.68</v>
       </c>
       <c r="K40">
-        <v>29.07</v>
+        <v>173.68</v>
       </c>
       <c r="L40" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="M40">
         <v>0</v>
@@ -26681,28 +26684,28 @@
         <v>961</v>
       </c>
       <c r="E41" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="F41">
-        <v>95.650999999999897</v>
+        <v>19.6419999999999</v>
       </c>
       <c r="G41" t="s">
         <v>18</v>
       </c>
       <c r="H41">
-        <v>1.64</v>
+        <v>1.42</v>
       </c>
       <c r="I41">
-        <v>156.87</v>
+        <v>27.89</v>
       </c>
       <c r="J41">
-        <v>1.69</v>
+        <v>1.48</v>
       </c>
       <c r="K41">
-        <v>161.65</v>
+        <v>29.07</v>
       </c>
       <c r="L41" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="M41">
         <v>0</v>
@@ -26713,19 +26716,19 @@
         <v>55</v>
       </c>
       <c r="B42" t="s">
-        <v>97</v>
+        <v>151</v>
       </c>
       <c r="C42" t="s">
-        <v>946</v>
+        <v>960</v>
       </c>
       <c r="D42" t="s">
-        <v>947</v>
+        <v>961</v>
       </c>
       <c r="E42" t="s">
         <v>17</v>
       </c>
       <c r="F42">
-        <v>64.141999999999896</v>
+        <v>95.650999999999897</v>
       </c>
       <c r="G42" t="s">
         <v>18</v>
@@ -26734,18 +26737,59 @@
         <v>1.64</v>
       </c>
       <c r="I42">
-        <v>105.19</v>
+        <v>156.87</v>
       </c>
       <c r="J42">
         <v>1.69</v>
       </c>
       <c r="K42">
+        <v>161.65</v>
+      </c>
+      <c r="L42" t="s">
+        <v>991</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>55</v>
+      </c>
+      <c r="B43" t="s">
+        <v>97</v>
+      </c>
+      <c r="C43" t="s">
+        <v>946</v>
+      </c>
+      <c r="D43" t="s">
+        <v>947</v>
+      </c>
+      <c r="E43" t="s">
+        <v>17</v>
+      </c>
+      <c r="F43">
+        <v>64.141999999999896</v>
+      </c>
+      <c r="G43" t="s">
+        <v>18</v>
+      </c>
+      <c r="H43">
+        <v>1.64</v>
+      </c>
+      <c r="I43">
+        <v>105.19</v>
+      </c>
+      <c r="J43">
+        <v>1.69</v>
+      </c>
+      <c r="K43">
         <v>108.4</v>
       </c>
-      <c r="L42" t="s">
-        <v>990</v>
-      </c>
-      <c r="M42">
+      <c r="L43" t="s">
+        <v>992</v>
+      </c>
+      <c r="M43">
         <v>0</v>
       </c>
     </row>
@@ -26808,10 +26852,10 @@
         <v>97</v>
       </c>
       <c r="C2" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="D2" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="E2" t="s">
         <v>17</v>
@@ -26835,7 +26879,7 @@
         <v>20</v>
       </c>
       <c r="L2" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -26849,10 +26893,10 @@
         <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="D3" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="E3" t="s">
         <v>17</v>
@@ -26890,10 +26934,10 @@
         <v>442</v>
       </c>
       <c r="C4" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="D4" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="E4" t="s">
         <v>17</v>
@@ -26931,10 +26975,10 @@
         <v>162</v>
       </c>
       <c r="C5" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="D5" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="E5" t="s">
         <v>17</v>
@@ -26958,7 +27002,7 @@
         <v>35.01</v>
       </c>
       <c r="L5" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="M5">
         <v>0</v>
@@ -26972,10 +27016,10 @@
         <v>294</v>
       </c>
       <c r="C6" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="D6" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="E6" t="s">
         <v>17</v>
@@ -26999,7 +27043,7 @@
         <v>24.45</v>
       </c>
       <c r="L6" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="M6">
         <v>0</v>
@@ -27064,10 +27108,10 @@
         <v>93</v>
       </c>
       <c r="C2" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="D2" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="E2" t="s">
         <v>17</v>
@@ -27105,10 +27149,10 @@
         <v>702</v>
       </c>
       <c r="C3" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="D3" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="E3" t="s">
         <v>17</v>
@@ -27146,10 +27190,10 @@
         <v>97</v>
       </c>
       <c r="C4" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="D4" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="E4" t="s">
         <v>17</v>
@@ -27187,10 +27231,10 @@
         <v>375</v>
       </c>
       <c r="C5" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="D5" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="E5" t="s">
         <v>17</v>
@@ -27279,10 +27323,10 @@
         <v>208</v>
       </c>
       <c r="C2" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="D2" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="E2" t="s">
         <v>240</v>
@@ -27320,10 +27364,10 @@
         <v>208</v>
       </c>
       <c r="C3" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="D3" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="E3" t="s">
         <v>45</v>
@@ -27361,10 +27405,10 @@
         <v>155</v>
       </c>
       <c r="C4" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="D4" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="E4" t="s">
         <v>240</v>
@@ -27402,10 +27446,10 @@
         <v>204</v>
       </c>
       <c r="C5" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="D5" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="E5" t="s">
         <v>45</v>
@@ -27429,7 +27473,7 @@
         <v>38.369999999999997</v>
       </c>
       <c r="L5" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="M5">
         <v>0</v>
@@ -27443,10 +27487,10 @@
         <v>357</v>
       </c>
       <c r="C6" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="D6" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="E6" t="s">
         <v>45</v>
@@ -27484,10 +27528,10 @@
         <v>162</v>
       </c>
       <c r="C7" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="D7" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="E7" t="s">
         <v>17</v>
@@ -27511,7 +27555,7 @@
         <v>74.53</v>
       </c>
       <c r="L7" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="M7">
         <v>0</v>
@@ -27525,10 +27569,10 @@
         <v>147</v>
       </c>
       <c r="C8" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="D8" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="E8" t="s">
         <v>45</v>
@@ -27552,7 +27596,7 @@
         <v>24.87</v>
       </c>
       <c r="L8" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="M8">
         <v>0</v>
@@ -27566,10 +27610,10 @@
         <v>208</v>
       </c>
       <c r="C9" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="D9" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="E9" t="s">
         <v>45</v>
@@ -27607,10 +27651,10 @@
         <v>162</v>
       </c>
       <c r="C10" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="D10" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="E10" t="s">
         <v>45</v>
@@ -27634,7 +27678,7 @@
         <v>46.28</v>
       </c>
       <c r="L10" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="M10">
         <v>0</v>
@@ -27648,10 +27692,10 @@
         <v>260</v>
       </c>
       <c r="C11" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="D11" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="E11" t="s">
         <v>45</v>
@@ -27675,7 +27719,7 @@
         <v>48.94</v>
       </c>
       <c r="L11" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="M11">
         <v>0</v>
@@ -27689,10 +27733,10 @@
         <v>162</v>
       </c>
       <c r="C12" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="D12" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="E12" t="s">
         <v>45</v>
@@ -27716,7 +27760,7 @@
         <v>44.93</v>
       </c>
       <c r="L12" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="M12">
         <v>0</v>
@@ -27730,10 +27774,10 @@
         <v>208</v>
       </c>
       <c r="C13" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="D13" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="E13" t="s">
         <v>45</v>
@@ -27771,10 +27815,10 @@
         <v>162</v>
       </c>
       <c r="C14" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="D14" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="E14" t="s">
         <v>45</v>
@@ -27863,10 +27907,10 @@
         <v>162</v>
       </c>
       <c r="C2" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="D2" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="E2" t="s">
         <v>379</v>
@@ -27884,7 +27928,7 @@
         <v>30.75</v>
       </c>
       <c r="L2" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="M2">
         <v>1058</v>
@@ -27898,10 +27942,10 @@
         <v>162</v>
       </c>
       <c r="C3" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="D3" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="E3" t="s">
         <v>17</v>
@@ -27925,7 +27969,7 @@
         <v>49.88</v>
       </c>
       <c r="L3" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="M3">
         <v>0</v>
@@ -27939,10 +27983,10 @@
         <v>260</v>
       </c>
       <c r="C4" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="D4" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="E4" t="s">
         <v>379</v>
@@ -27974,10 +28018,10 @@
         <v>162</v>
       </c>
       <c r="C5" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="D5" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="E5" t="s">
         <v>379</v>
@@ -27995,7 +28039,7 @@
         <v>26.68</v>
       </c>
       <c r="L5" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="M5">
         <v>0</v>
@@ -28009,10 +28053,10 @@
         <v>162</v>
       </c>
       <c r="C6" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="D6" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="E6" t="s">
         <v>379</v>
@@ -28044,10 +28088,10 @@
         <v>162</v>
       </c>
       <c r="C7" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="D7" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="E7" t="s">
         <v>17</v>
@@ -28071,7 +28115,7 @@
         <v>56.43</v>
       </c>
       <c r="L7" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="M7">
         <v>203263</v>
@@ -28085,10 +28129,10 @@
         <v>162</v>
       </c>
       <c r="C8" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="D8" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="E8" t="s">
         <v>379</v>
@@ -28120,10 +28164,10 @@
         <v>162</v>
       </c>
       <c r="C9" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="D9" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="E9" t="s">
         <v>17</v>
@@ -28147,7 +28191,7 @@
         <v>54.87</v>
       </c>
       <c r="L9" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="M9">
         <v>0</v>
@@ -28161,10 +28205,10 @@
         <v>162</v>
       </c>
       <c r="C10" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="D10" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="E10" t="s">
         <v>379</v>
@@ -28196,10 +28240,10 @@
         <v>147</v>
       </c>
       <c r="C11" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="D11" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="E11" t="s">
         <v>17</v>
@@ -28223,7 +28267,7 @@
         <v>62.03</v>
       </c>
       <c r="L11" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="M11">
         <v>0</v>
@@ -28237,10 +28281,10 @@
         <v>162</v>
       </c>
       <c r="C12" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="D12" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="E12" t="s">
         <v>379</v>
@@ -28272,10 +28316,10 @@
         <v>208</v>
       </c>
       <c r="C13" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="D13" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="E13" t="s">
         <v>379</v>
@@ -28293,7 +28337,7 @@
         <v>19.25</v>
       </c>
       <c r="L13" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="M13">
         <v>0</v>
@@ -28307,10 +28351,10 @@
         <v>162</v>
       </c>
       <c r="C14" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="D14" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="E14" t="s">
         <v>379</v>
@@ -28328,7 +28372,7 @@
         <v>29.51</v>
       </c>
       <c r="L14" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="M14">
         <v>0</v>
@@ -28342,10 +28386,10 @@
         <v>208</v>
       </c>
       <c r="C15" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="D15" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="E15" t="s">
         <v>379</v>
@@ -28377,10 +28421,10 @@
         <v>162</v>
       </c>
       <c r="C16" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="D16" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="E16" t="s">
         <v>17</v>
@@ -28404,7 +28448,7 @@
         <v>60.82</v>
       </c>
       <c r="L16" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="M16">
         <v>0</v>
@@ -28418,10 +28462,10 @@
         <v>162</v>
       </c>
       <c r="C17" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="D17" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="E17" t="s">
         <v>45</v>
@@ -28459,10 +28503,10 @@
         <v>162</v>
       </c>
       <c r="C18" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="D18" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="E18" t="s">
         <v>379</v>
@@ -28494,10 +28538,10 @@
         <v>162</v>
       </c>
       <c r="C19" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="D19" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="E19" t="s">
         <v>17</v>
@@ -28535,10 +28579,10 @@
         <v>162</v>
       </c>
       <c r="C20" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="D20" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="E20" t="s">
         <v>379</v>
@@ -28570,10 +28614,10 @@
         <v>208</v>
       </c>
       <c r="C21" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="D21" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="E21" t="s">
         <v>379</v>
@@ -28605,10 +28649,10 @@
         <v>162</v>
       </c>
       <c r="C22" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="D22" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="E22" t="s">
         <v>379</v>
@@ -28626,7 +28670,7 @@
         <v>27.74</v>
       </c>
       <c r="L22" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="M22">
         <v>0</v>
@@ -28640,10 +28684,10 @@
         <v>62</v>
       </c>
       <c r="C23" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="D23" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="E23" t="s">
         <v>379</v>
@@ -28675,10 +28719,10 @@
         <v>442</v>
       </c>
       <c r="C24" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="D24" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="E24" t="s">
         <v>379</v>
@@ -28710,10 +28754,10 @@
         <v>162</v>
       </c>
       <c r="C25" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="D25" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="E25" t="s">
         <v>17</v>
@@ -28751,10 +28795,10 @@
         <v>162</v>
       </c>
       <c r="C26" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="D26" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="E26" t="s">
         <v>379</v>
@@ -28786,10 +28830,10 @@
         <v>208</v>
       </c>
       <c r="C27" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="D27" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="E27" t="s">
         <v>379</v>
@@ -28822,9 +28866,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2500-000000000000}">
   <dimension ref="A1:M103"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -28875,10 +28916,10 @@
         <v>151</v>
       </c>
       <c r="C2" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="D2" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="E2" t="s">
         <v>17</v>
@@ -28902,7 +28943,7 @@
         <v>80.37</v>
       </c>
       <c r="L2" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -28916,10 +28957,10 @@
         <v>93</v>
       </c>
       <c r="C3" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="D3" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="E3" t="s">
         <v>17</v>
@@ -28943,7 +28984,7 @@
         <v>248.9</v>
       </c>
       <c r="L3" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="M3">
         <v>152744</v>
@@ -28957,10 +28998,10 @@
         <v>432</v>
       </c>
       <c r="C4" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="D4" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="E4" t="s">
         <v>17</v>
@@ -28998,10 +29039,10 @@
         <v>93</v>
       </c>
       <c r="C5" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="D5" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="E5" t="s">
         <v>17</v>
@@ -29039,10 +29080,10 @@
         <v>380</v>
       </c>
       <c r="C6" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="D6" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="E6" t="s">
         <v>17</v>
@@ -29080,10 +29121,10 @@
         <v>93</v>
       </c>
       <c r="C7" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="D7" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="E7" t="s">
         <v>17</v>
@@ -29121,10 +29162,10 @@
         <v>93</v>
       </c>
       <c r="C8" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="D8" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="E8" t="s">
         <v>17</v>
@@ -29162,10 +29203,10 @@
         <v>93</v>
       </c>
       <c r="C9" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="D9" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="E9" t="s">
         <v>17</v>
@@ -29203,10 +29244,10 @@
         <v>432</v>
       </c>
       <c r="C10" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="D10" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="E10" t="s">
         <v>17</v>
@@ -29230,7 +29271,7 @@
         <v>48.41</v>
       </c>
       <c r="L10" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="M10">
         <v>0</v>
@@ -29244,10 +29285,10 @@
         <v>93</v>
       </c>
       <c r="C11" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="D11" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="E11" t="s">
         <v>17</v>
@@ -29271,7 +29312,7 @@
         <v>133</v>
       </c>
       <c r="L11" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="M11">
         <v>0</v>
@@ -29285,10 +29326,10 @@
         <v>93</v>
       </c>
       <c r="C12" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="D12" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="E12" t="s">
         <v>17</v>
@@ -29312,7 +29353,7 @@
         <v>226.1</v>
       </c>
       <c r="L12" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="M12">
         <v>227750</v>
@@ -29326,10 +29367,10 @@
         <v>380</v>
       </c>
       <c r="C13" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="D13" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="E13" t="s">
         <v>17</v>
@@ -29367,10 +29408,10 @@
         <v>375</v>
       </c>
       <c r="C14" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="D14" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="E14" t="s">
         <v>17</v>
@@ -29408,10 +29449,10 @@
         <v>97</v>
       </c>
       <c r="C15" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="D15" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="E15" t="s">
         <v>17</v>
@@ -29449,10 +29490,10 @@
         <v>501</v>
       </c>
       <c r="C16" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="D16" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="E16" t="s">
         <v>45</v>
@@ -29476,7 +29517,7 @@
         <v>49.56</v>
       </c>
       <c r="L16" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="M16">
         <v>0</v>
@@ -29490,10 +29531,10 @@
         <v>62</v>
       </c>
       <c r="C17" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="D17" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="E17" t="s">
         <v>240</v>
@@ -29517,7 +29558,7 @@
         <v>34.72</v>
       </c>
       <c r="L17" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="M17">
         <v>0</v>
@@ -29531,10 +29572,10 @@
         <v>432</v>
       </c>
       <c r="C18" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="D18" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="E18" t="s">
         <v>17</v>
@@ -29572,10 +29613,10 @@
         <v>432</v>
       </c>
       <c r="C19" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="D19" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="E19" t="s">
         <v>179</v>
@@ -29613,10 +29654,10 @@
         <v>93</v>
       </c>
       <c r="C20" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="D20" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="E20" t="s">
         <v>17</v>
@@ -29640,7 +29681,7 @@
         <v>306.45999999999998</v>
       </c>
       <c r="L20" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="M20">
         <v>0</v>
@@ -29654,10 +29695,10 @@
         <v>93</v>
       </c>
       <c r="C21" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="D21" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="E21" t="s">
         <v>17</v>
@@ -29695,10 +29736,10 @@
         <v>93</v>
       </c>
       <c r="C22" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="D22" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="E22" t="s">
         <v>17</v>
@@ -29736,10 +29777,10 @@
         <v>93</v>
       </c>
       <c r="C23" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="D23" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="E23" t="s">
         <v>17</v>
@@ -29777,10 +29818,10 @@
         <v>93</v>
       </c>
       <c r="C24" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="D24" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="E24" t="s">
         <v>240</v>
@@ -29818,10 +29859,10 @@
         <v>97</v>
       </c>
       <c r="C25" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="D25" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="E25" t="s">
         <v>17</v>
@@ -29859,10 +29900,10 @@
         <v>93</v>
       </c>
       <c r="C26" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="D26" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="E26" t="s">
         <v>17</v>
@@ -29886,7 +29927,7 @@
         <v>60.86</v>
       </c>
       <c r="L26" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="M26">
         <v>0</v>
@@ -29900,10 +29941,10 @@
         <v>93</v>
       </c>
       <c r="C27" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="D27" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="E27" t="s">
         <v>17</v>
@@ -29927,7 +29968,7 @@
         <v>165.6</v>
       </c>
       <c r="L27" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="M27">
         <v>0</v>
@@ -29941,10 +29982,10 @@
         <v>93</v>
       </c>
       <c r="C28" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="D28" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="E28" t="s">
         <v>17</v>
@@ -29968,7 +30009,7 @@
         <v>241.51</v>
       </c>
       <c r="L28" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="M28">
         <v>152884</v>
@@ -29982,10 +30023,10 @@
         <v>385</v>
       </c>
       <c r="C29" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="D29" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="E29" t="s">
         <v>240</v>
@@ -30023,10 +30064,10 @@
         <v>294</v>
       </c>
       <c r="C30" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="D30" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="E30" t="s">
         <v>17</v>
@@ -30064,10 +30105,10 @@
         <v>432</v>
       </c>
       <c r="C31" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="D31" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="E31" t="s">
         <v>17</v>
@@ -30105,10 +30146,10 @@
         <v>432</v>
       </c>
       <c r="C32" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="D32" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="E32" t="s">
         <v>17</v>
@@ -30132,7 +30173,7 @@
         <v>113.43</v>
       </c>
       <c r="L32" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="M32">
         <v>0</v>
@@ -30146,10 +30187,10 @@
         <v>380</v>
       </c>
       <c r="C33" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="D33" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="E33" t="s">
         <v>17</v>
@@ -30187,10 +30228,10 @@
         <v>97</v>
       </c>
       <c r="C34" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="D34" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="E34" t="s">
         <v>17</v>
@@ -30228,10 +30269,10 @@
         <v>501</v>
       </c>
       <c r="C35" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="D35" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="E35" t="s">
         <v>45</v>
@@ -30269,10 +30310,10 @@
         <v>93</v>
       </c>
       <c r="C36" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="D36" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="E36" t="s">
         <v>17</v>
@@ -30310,10 +30351,10 @@
         <v>93</v>
       </c>
       <c r="C37" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="D37" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="E37" t="s">
         <v>17</v>
@@ -30351,10 +30392,10 @@
         <v>93</v>
       </c>
       <c r="C38" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="D38" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="E38" t="s">
         <v>17</v>
@@ -30392,10 +30433,10 @@
         <v>93</v>
       </c>
       <c r="C39" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="D39" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="E39" t="s">
         <v>17</v>
@@ -30433,10 +30474,10 @@
         <v>93</v>
       </c>
       <c r="C40" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="D40" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="E40" t="s">
         <v>17</v>
@@ -30460,7 +30501,7 @@
         <v>543.92999999999995</v>
       </c>
       <c r="L40" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="M40">
         <v>0</v>
@@ -30474,10 +30515,10 @@
         <v>97</v>
       </c>
       <c r="C41" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="D41" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="E41" t="s">
         <v>17</v>
@@ -30501,7 +30542,7 @@
         <v>330.6</v>
       </c>
       <c r="L41" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="M41">
         <v>0</v>
@@ -30515,10 +30556,10 @@
         <v>93</v>
       </c>
       <c r="C42" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="D42" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="E42" t="s">
         <v>17</v>
@@ -30556,10 +30597,10 @@
         <v>93</v>
       </c>
       <c r="C43" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="D43" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="E43" t="s">
         <v>45</v>
@@ -30583,7 +30624,7 @@
         <v>57.89</v>
       </c>
       <c r="L43" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="M43">
         <v>0</v>
@@ -30597,10 +30638,10 @@
         <v>75</v>
       </c>
       <c r="C44" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="D44" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="E44" t="s">
         <v>17</v>
@@ -30638,10 +30679,10 @@
         <v>93</v>
       </c>
       <c r="C45" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="D45" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="E45" t="s">
         <v>45</v>
@@ -30665,7 +30706,7 @@
         <v>46.24</v>
       </c>
       <c r="L45" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="M45">
         <v>320946</v>
@@ -30679,10 +30720,10 @@
         <v>93</v>
       </c>
       <c r="C46" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="D46" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="E46" t="s">
         <v>17</v>
@@ -30706,7 +30747,7 @@
         <v>70.03</v>
       </c>
       <c r="L46" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="M46">
         <v>0</v>
@@ -30720,10 +30761,10 @@
         <v>93</v>
       </c>
       <c r="C47" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="D47" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="E47" t="s">
         <v>17</v>
@@ -30747,7 +30788,7 @@
         <v>356.11</v>
       </c>
       <c r="L47" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="M47">
         <v>0</v>
@@ -30761,10 +30802,10 @@
         <v>93</v>
       </c>
       <c r="C48" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="D48" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="E48" t="s">
         <v>17</v>
@@ -30802,10 +30843,10 @@
         <v>93</v>
       </c>
       <c r="C49" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="D49" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="E49" t="s">
         <v>17</v>
@@ -30843,10 +30884,10 @@
         <v>93</v>
       </c>
       <c r="C50" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="D50" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="E50" t="s">
         <v>17</v>
@@ -30870,7 +30911,7 @@
         <v>255</v>
       </c>
       <c r="L50" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="M50">
         <v>153022</v>
@@ -30884,10 +30925,10 @@
         <v>93</v>
       </c>
       <c r="C51" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="D51" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="E51" t="s">
         <v>240</v>
@@ -30925,10 +30966,10 @@
         <v>93</v>
       </c>
       <c r="C52" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="D52" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="E52" t="s">
         <v>17</v>
@@ -30966,10 +31007,10 @@
         <v>93</v>
       </c>
       <c r="C53" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="D53" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="E53" t="s">
         <v>17</v>
@@ -31007,10 +31048,10 @@
         <v>93</v>
       </c>
       <c r="C54" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="D54" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="E54" t="s">
         <v>17</v>
@@ -31048,10 +31089,10 @@
         <v>380</v>
       </c>
       <c r="C55" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="D55" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="E55" t="s">
         <v>17</v>
@@ -31089,10 +31130,10 @@
         <v>442</v>
       </c>
       <c r="C56" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="D56" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="E56" t="s">
         <v>17</v>
@@ -31116,7 +31157,7 @@
         <v>400.15</v>
       </c>
       <c r="L56" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="M56">
         <v>187120</v>
@@ -31130,10 +31171,10 @@
         <v>93</v>
       </c>
       <c r="C57" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="D57" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="E57" t="s">
         <v>17</v>
@@ -31157,7 +31198,7 @@
         <v>340.34</v>
       </c>
       <c r="L57" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="M57">
         <v>95652</v>
@@ -31171,10 +31212,10 @@
         <v>93</v>
       </c>
       <c r="C58" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="D58" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="E58" t="s">
         <v>17</v>
@@ -31212,10 +31253,10 @@
         <v>380</v>
       </c>
       <c r="C59" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="D59" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="E59" t="s">
         <v>17</v>
@@ -31239,7 +31280,7 @@
         <v>354.46</v>
       </c>
       <c r="L59" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="M59">
         <v>0</v>
@@ -31253,10 +31294,10 @@
         <v>93</v>
       </c>
       <c r="C60" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="D60" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="E60" t="s">
         <v>17</v>
@@ -31280,7 +31321,7 @@
         <v>477.45</v>
       </c>
       <c r="L60" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="M60">
         <v>0</v>
@@ -31294,10 +31335,10 @@
         <v>93</v>
       </c>
       <c r="C61" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="D61" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="E61" t="s">
         <v>45</v>
@@ -31335,10 +31376,10 @@
         <v>93</v>
       </c>
       <c r="C62" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="D62" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="E62" t="s">
         <v>17</v>
@@ -31376,10 +31417,10 @@
         <v>380</v>
       </c>
       <c r="C63" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="D63" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="E63" t="s">
         <v>17</v>
@@ -31417,10 +31458,10 @@
         <v>375</v>
       </c>
       <c r="C64" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="D64" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="E64" t="s">
         <v>17</v>
@@ -31458,10 +31499,10 @@
         <v>501</v>
       </c>
       <c r="C65" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="D65" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="E65" t="s">
         <v>17</v>
@@ -31485,7 +31526,7 @@
         <v>69.81</v>
       </c>
       <c r="L65" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="M65">
         <v>0</v>
@@ -31499,10 +31540,10 @@
         <v>93</v>
       </c>
       <c r="C66" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="D66" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="E66" t="s">
         <v>17</v>
@@ -31526,7 +31567,7 @@
         <v>156</v>
       </c>
       <c r="L66" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="M66">
         <v>0</v>
@@ -31540,10 +31581,10 @@
         <v>93</v>
       </c>
       <c r="C67" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="D67" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="E67" t="s">
         <v>17</v>
@@ -31581,10 +31622,10 @@
         <v>93</v>
       </c>
       <c r="C68" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="D68" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="E68" t="s">
         <v>17</v>
@@ -31622,10 +31663,10 @@
         <v>93</v>
       </c>
       <c r="C69" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="D69" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="E69" t="s">
         <v>17</v>
@@ -31649,7 +31690,7 @@
         <v>320.27999999999997</v>
       </c>
       <c r="L69" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="M69">
         <v>0</v>
@@ -31663,10 +31704,10 @@
         <v>93</v>
       </c>
       <c r="C70" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="D70" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="E70" t="s">
         <v>17</v>
@@ -31690,7 +31731,7 @@
         <v>282.60000000000002</v>
       </c>
       <c r="L70" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="M70">
         <v>228888</v>
@@ -31704,10 +31745,10 @@
         <v>375</v>
       </c>
       <c r="C71" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="D71" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="E71" t="s">
         <v>17</v>
@@ -31745,10 +31786,10 @@
         <v>375</v>
       </c>
       <c r="C72" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="D72" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="E72" t="s">
         <v>17</v>
@@ -31772,7 +31813,7 @@
         <v>93.6</v>
       </c>
       <c r="L72" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="M72">
         <v>242400</v>
@@ -31786,10 +31827,10 @@
         <v>442</v>
       </c>
       <c r="C73" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="D73" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="E73" t="s">
         <v>45</v>
@@ -31827,10 +31868,10 @@
         <v>93</v>
       </c>
       <c r="C74" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="D74" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="E74" t="s">
         <v>17</v>
@@ -31854,7 +31895,7 @@
         <v>104.94</v>
       </c>
       <c r="L74" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="M74">
         <v>493443</v>
@@ -31868,10 +31909,10 @@
         <v>380</v>
       </c>
       <c r="C75" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="D75" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="E75" t="s">
         <v>17</v>
@@ -31909,10 +31950,10 @@
         <v>432</v>
       </c>
       <c r="C76" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="D76" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="E76" t="s">
         <v>17</v>
@@ -31950,10 +31991,10 @@
         <v>93</v>
       </c>
       <c r="C77" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="D77" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="E77" t="s">
         <v>17</v>
@@ -31977,7 +32018,7 @@
         <v>463.68</v>
       </c>
       <c r="L77" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="M77">
         <v>0</v>
@@ -31991,10 +32032,10 @@
         <v>375</v>
       </c>
       <c r="C78" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="D78" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="E78" t="s">
         <v>45</v>
@@ -32032,10 +32073,10 @@
         <v>93</v>
       </c>
       <c r="C79" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="D79" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="E79" t="s">
         <v>17</v>
@@ -32073,10 +32114,10 @@
         <v>93</v>
       </c>
       <c r="C80" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="D80" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="E80" t="s">
         <v>17</v>
@@ -32100,7 +32141,7 @@
         <v>322</v>
       </c>
       <c r="L80" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="M80">
         <v>0</v>
@@ -32114,10 +32155,10 @@
         <v>93</v>
       </c>
       <c r="C81" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="D81" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="E81" t="s">
         <v>17</v>
@@ -32141,7 +32182,7 @@
         <v>249.39</v>
       </c>
       <c r="L81" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="M81">
         <v>170268</v>
@@ -32155,10 +32196,10 @@
         <v>93</v>
       </c>
       <c r="C82" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="D82" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="E82" t="s">
         <v>17</v>
@@ -32182,7 +32223,7 @@
         <v>281.75</v>
       </c>
       <c r="L82" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="M82">
         <v>229303</v>
@@ -32196,10 +32237,10 @@
         <v>501</v>
       </c>
       <c r="C83" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="D83" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="E83" t="s">
         <v>45</v>
@@ -32223,7 +32264,7 @@
         <v>44.65</v>
       </c>
       <c r="L83" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="M83">
         <v>0</v>
@@ -32237,10 +32278,10 @@
         <v>93</v>
       </c>
       <c r="C84" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="D84" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="E84" t="s">
         <v>17</v>
@@ -32264,7 +32305,7 @@
         <v>193.36</v>
       </c>
       <c r="L84" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="M84">
         <v>0</v>
@@ -32278,10 +32319,10 @@
         <v>380</v>
       </c>
       <c r="C85" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="D85" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="E85" t="s">
         <v>17</v>
@@ -32319,10 +32360,10 @@
         <v>432</v>
       </c>
       <c r="C86" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="D86" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="E86" t="s">
         <v>17</v>
@@ -32346,7 +32387,7 @@
         <v>94.66</v>
       </c>
       <c r="L86" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="M86">
         <v>0</v>
@@ -32360,10 +32401,10 @@
         <v>93</v>
       </c>
       <c r="C87" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="D87" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="E87" t="s">
         <v>17</v>
@@ -32401,10 +32442,10 @@
         <v>93</v>
       </c>
       <c r="C88" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="D88" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="E88" t="s">
         <v>17</v>
@@ -32442,10 +32483,10 @@
         <v>93</v>
       </c>
       <c r="C89" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="D89" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="E89" t="s">
         <v>17</v>
@@ -32483,10 +32524,10 @@
         <v>380</v>
       </c>
       <c r="C90" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="D90" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="E90" t="s">
         <v>17</v>
@@ -32510,7 +32551,7 @@
         <v>388.84</v>
       </c>
       <c r="L90" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="M90">
         <v>0</v>
@@ -32524,10 +32565,10 @@
         <v>380</v>
       </c>
       <c r="C91" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="D91" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="E91" t="s">
         <v>17</v>
@@ -32565,10 +32606,10 @@
         <v>93</v>
       </c>
       <c r="C92" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="D92" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="E92" t="s">
         <v>45</v>
@@ -32606,10 +32647,10 @@
         <v>380</v>
       </c>
       <c r="C93" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="D93" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="E93" t="s">
         <v>17</v>
@@ -32633,7 +32674,7 @@
         <v>288.38</v>
       </c>
       <c r="L93" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="M93">
         <v>96428</v>
@@ -32647,10 +32688,10 @@
         <v>380</v>
       </c>
       <c r="C94" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="D94" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="E94" t="s">
         <v>17</v>
@@ -32674,7 +32715,7 @@
         <v>301.42</v>
       </c>
       <c r="L94" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="M94">
         <v>171051</v>
@@ -32688,10 +32729,10 @@
         <v>380</v>
       </c>
       <c r="C95" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="D95" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="E95" t="s">
         <v>17</v>
@@ -32729,10 +32770,10 @@
         <v>93</v>
       </c>
       <c r="C96" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="D96" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="E96" t="s">
         <v>17</v>
@@ -32756,7 +32797,7 @@
         <v>330.02</v>
       </c>
       <c r="L96" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="M96">
         <v>0</v>
@@ -32770,10 +32811,10 @@
         <v>93</v>
       </c>
       <c r="C97" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="D97" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="E97" t="s">
         <v>17</v>
@@ -32797,7 +32838,7 @@
         <v>300.82</v>
       </c>
       <c r="L97" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="M97">
         <v>153325</v>
@@ -32811,10 +32852,10 @@
         <v>93</v>
       </c>
       <c r="C98" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="D98" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="E98" t="s">
         <v>17</v>
@@ -32852,10 +32893,10 @@
         <v>93</v>
       </c>
       <c r="C99" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="D99" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="E99" t="s">
         <v>17</v>
@@ -32893,10 +32934,10 @@
         <v>93</v>
       </c>
       <c r="C100" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="D100" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="E100" t="s">
         <v>17</v>
@@ -32920,7 +32961,7 @@
         <v>338</v>
       </c>
       <c r="L100" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="M100">
         <v>0</v>
@@ -32934,10 +32975,10 @@
         <v>375</v>
       </c>
       <c r="C101" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="D101" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="E101" t="s">
         <v>17</v>
@@ -32961,7 +33002,7 @@
         <v>106.47</v>
       </c>
       <c r="L101" t="s">
-        <v>1115</v>
+        <v>1117</v>
       </c>
       <c r="M101">
         <v>494148</v>
@@ -32975,10 +33016,10 @@
         <v>97</v>
       </c>
       <c r="C102" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="D102" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="E102" t="s">
         <v>240</v>
@@ -33002,7 +33043,7 @@
         <v>93.63</v>
       </c>
       <c r="L102" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="M102">
         <v>0</v>
@@ -33016,10 +33057,10 @@
         <v>501</v>
       </c>
       <c r="C103" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="D103" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="E103" t="s">
         <v>45</v>
@@ -33043,7 +33084,7 @@
         <v>57.17</v>
       </c>
       <c r="L103" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="M103">
         <v>0</v>
@@ -33108,10 +33149,10 @@
         <v>93</v>
       </c>
       <c r="C2" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="D2" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="E2" t="s">
         <v>17</v>
@@ -33149,10 +33190,10 @@
         <v>93</v>
       </c>
       <c r="C3" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="D3" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="E3" t="s">
         <v>17</v>
@@ -33190,10 +33231,10 @@
         <v>93</v>
       </c>
       <c r="C4" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="D4" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="E4" t="s">
         <v>17</v>
@@ -33217,7 +33258,7 @@
         <v>101.57</v>
       </c>
       <c r="L4" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="M4">
         <v>0</v>
@@ -33231,10 +33272,10 @@
         <v>93</v>
       </c>
       <c r="C5" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="D5" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="E5" t="s">
         <v>17</v>
@@ -33272,10 +33313,10 @@
         <v>93</v>
       </c>
       <c r="C6" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="D6" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="E6" t="s">
         <v>17</v>
@@ -33313,10 +33354,10 @@
         <v>93</v>
       </c>
       <c r="C7" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="D7" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="E7" t="s">
         <v>17</v>
@@ -33354,10 +33395,10 @@
         <v>93</v>
       </c>
       <c r="C8" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="D8" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="E8" t="s">
         <v>17</v>
@@ -33381,7 +33422,7 @@
         <v>75.78</v>
       </c>
       <c r="L8" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="M8">
         <v>418765</v>
@@ -33395,10 +33436,10 @@
         <v>93</v>
       </c>
       <c r="C9" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="D9" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="E9" t="s">
         <v>17</v>
@@ -33422,7 +33463,7 @@
         <v>89.15</v>
       </c>
       <c r="L9" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="M9">
         <v>419227</v>
@@ -33436,10 +33477,10 @@
         <v>151</v>
       </c>
       <c r="C10" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="D10" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="E10" t="s">
         <v>17</v>
@@ -33477,10 +33518,10 @@
         <v>432</v>
       </c>
       <c r="C11" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="D11" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="E11" t="s">
         <v>17</v>
@@ -33504,7 +33545,7 @@
         <v>55.61</v>
       </c>
       <c r="L11" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="M11">
         <v>174141</v>
@@ -33518,10 +33559,10 @@
         <v>93</v>
       </c>
       <c r="C12" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="D12" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="E12" t="s">
         <v>17</v>
@@ -33545,7 +33586,7 @@
         <v>40.82</v>
       </c>
       <c r="L12" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="M12">
         <v>419839</v>
@@ -33559,10 +33600,10 @@
         <v>93</v>
       </c>
       <c r="C13" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="D13" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="E13" t="s">
         <v>17</v>
@@ -33600,10 +33641,10 @@
         <v>93</v>
       </c>
       <c r="C14" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="D14" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="E14" t="s">
         <v>17</v>
@@ -33641,10 +33682,10 @@
         <v>97</v>
       </c>
       <c r="C15" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="D15" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="E15" t="s">
         <v>17</v>
@@ -33668,7 +33709,7 @@
         <v>31.57</v>
       </c>
       <c r="L15" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="M15">
         <v>174388</v>
@@ -33907,10 +33948,10 @@
         <v>93</v>
       </c>
       <c r="C2" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="D2" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="E2" t="s">
         <v>17</v>
@@ -33948,10 +33989,10 @@
         <v>166</v>
       </c>
       <c r="C3" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="D3" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="E3" t="s">
         <v>17</v>
@@ -33989,10 +34030,10 @@
         <v>93</v>
       </c>
       <c r="C4" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="D4" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="E4" t="s">
         <v>17</v>
@@ -34016,7 +34057,7 @@
         <v>96.43</v>
       </c>
       <c r="L4" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="M4">
         <v>178835</v>
@@ -34033,7 +34074,7 @@
         <v>497</v>
       </c>
       <c r="D5" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="E5" t="s">
         <v>17</v>
@@ -34057,7 +34098,7 @@
         <v>79.2</v>
       </c>
       <c r="L5" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="M5">
         <v>0</v>
@@ -34071,10 +34112,10 @@
         <v>495</v>
       </c>
       <c r="C6" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="D6" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="E6" t="s">
         <v>17</v>
@@ -34098,7 +34139,7 @@
         <v>49.5</v>
       </c>
       <c r="L6" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="M6">
         <v>410214</v>
@@ -34112,10 +34153,10 @@
         <v>408</v>
       </c>
       <c r="C7" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="D7" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="E7" t="s">
         <v>17</v>
@@ -34139,7 +34180,7 @@
         <v>74.290000000000006</v>
       </c>
       <c r="L7" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="M7">
         <v>194645</v>
@@ -34153,10 +34194,10 @@
         <v>93</v>
       </c>
       <c r="C8" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="D8" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="E8" t="s">
         <v>17</v>
@@ -34194,10 +34235,10 @@
         <v>93</v>
       </c>
       <c r="C9" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="D9" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="E9" t="s">
         <v>17</v>
@@ -34235,10 +34276,10 @@
         <v>380</v>
       </c>
       <c r="C10" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="D10" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="E10" t="s">
         <v>17</v>
@@ -34276,10 +34317,10 @@
         <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="D11" t="s">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="E11" t="s">
         <v>17</v>
@@ -34303,7 +34344,7 @@
         <v>81.44</v>
       </c>
       <c r="L11" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="M11">
         <v>226108</v>
@@ -34317,10 +34358,10 @@
         <v>501</v>
       </c>
       <c r="C12" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="D12" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="E12" t="s">
         <v>17</v>
@@ -34344,7 +34385,7 @@
         <v>74.739999999999995</v>
       </c>
       <c r="L12" t="s">
-        <v>1143</v>
+        <v>1145</v>
       </c>
       <c r="M12">
         <v>410521</v>
@@ -34358,10 +34399,10 @@
         <v>166</v>
       </c>
       <c r="C13" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="D13" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="E13" t="s">
         <v>17</v>
@@ -34385,7 +34426,7 @@
         <v>78.510000000000005</v>
       </c>
       <c r="L13" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="M13">
         <v>195191</v>
@@ -34399,10 +34440,10 @@
         <v>93</v>
       </c>
       <c r="C14" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="D14" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="E14" t="s">
         <v>17</v>
@@ -34426,7 +34467,7 @@
         <v>86.28</v>
       </c>
       <c r="L14" t="s">
-        <v>1145</v>
+        <v>1147</v>
       </c>
       <c r="M14">
         <v>179389</v>
@@ -34440,10 +34481,10 @@
         <v>93</v>
       </c>
       <c r="C15" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="D15" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="E15" t="s">
         <v>17</v>
@@ -34467,7 +34508,7 @@
         <v>27</v>
       </c>
       <c r="L15" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="M15">
         <v>671113</v>
@@ -34481,10 +34522,10 @@
         <v>93</v>
       </c>
       <c r="C16" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="D16" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="E16" t="s">
         <v>17</v>
@@ -34522,10 +34563,10 @@
         <v>375</v>
       </c>
       <c r="C17" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
       <c r="D17" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
       <c r="E17" t="s">
         <v>45</v>
@@ -34563,10 +34604,10 @@
         <v>155</v>
       </c>
       <c r="C18" t="s">
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="D18" t="s">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="E18" t="s">
         <v>45</v>
@@ -34604,10 +34645,10 @@
         <v>93</v>
       </c>
       <c r="C19" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="D19" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="E19" t="s">
         <v>17</v>
@@ -34631,7 +34672,7 @@
         <v>13.8</v>
       </c>
       <c r="L19" t="s">
-        <v>1153</v>
+        <v>1155</v>
       </c>
       <c r="M19">
         <v>0</v>
@@ -34645,10 +34686,10 @@
         <v>432</v>
       </c>
       <c r="C20" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="D20" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="E20" t="s">
         <v>17</v>
@@ -34672,7 +34713,7 @@
         <v>95.61</v>
       </c>
       <c r="L20" t="s">
-        <v>1154</v>
+        <v>1156</v>
       </c>
       <c r="M20">
         <v>230802</v>
@@ -34689,7 +34730,7 @@
         <v>497</v>
       </c>
       <c r="D21" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="E21" t="s">
         <v>17</v>
@@ -34713,7 +34754,7 @@
         <v>82.71</v>
       </c>
       <c r="L21" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="M21">
         <v>0</v>
@@ -34727,10 +34768,10 @@
         <v>93</v>
       </c>
       <c r="C22" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="D22" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="E22" t="s">
         <v>17</v>
@@ -34768,10 +34809,10 @@
         <v>290</v>
       </c>
       <c r="C23" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="D23" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="E23" t="s">
         <v>17</v>
@@ -34806,13 +34847,13 @@
         <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="C24" t="s">
         <v>497</v>
       </c>
       <c r="D24" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="E24" t="s">
         <v>17</v>
@@ -34850,10 +34891,10 @@
         <v>754</v>
       </c>
       <c r="C25" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="D25" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="E25" t="s">
         <v>17</v>
@@ -34891,10 +34932,10 @@
         <v>93</v>
       </c>
       <c r="C26" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="D26" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="E26" t="s">
         <v>17</v>
@@ -34932,10 +34973,10 @@
         <v>351</v>
       </c>
       <c r="C27" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="D27" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="E27" t="s">
         <v>17</v>
@@ -34959,7 +35000,7 @@
         <v>454.55</v>
       </c>
       <c r="L27" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="M27">
         <v>993508</v>
@@ -34973,10 +35014,10 @@
         <v>75</v>
       </c>
       <c r="C28" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="D28" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="E28" t="s">
         <v>17</v>
@@ -35000,7 +35041,7 @@
         <v>93.11</v>
       </c>
       <c r="L28" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="M28">
         <v>361742</v>
@@ -35017,7 +35058,7 @@
         <v>497</v>
       </c>
       <c r="D29" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="E29" t="s">
         <v>17</v>
@@ -35055,10 +35096,10 @@
         <v>93</v>
       </c>
       <c r="C30" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="D30" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="E30" t="s">
         <v>17</v>
@@ -35082,7 +35123,7 @@
         <v>91.28</v>
       </c>
       <c r="L30" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="M30">
         <v>231403</v>
@@ -35096,10 +35137,10 @@
         <v>93</v>
       </c>
       <c r="C31" t="s">
-        <v>1160</v>
+        <v>1162</v>
       </c>
       <c r="D31" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="E31" t="s">
         <v>17</v>
@@ -35123,7 +35164,7 @@
         <v>97.8</v>
       </c>
       <c r="L31" t="s">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="M31">
         <v>56192</v>
@@ -35137,10 +35178,10 @@
         <v>93</v>
       </c>
       <c r="C32" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="D32" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="E32" t="s">
         <v>17</v>
@@ -35164,7 +35205,7 @@
         <v>84.59</v>
       </c>
       <c r="L32" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="M32">
         <v>411132</v>
@@ -35178,10 +35219,10 @@
         <v>70</v>
       </c>
       <c r="C33" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="D33" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="E33" t="s">
         <v>17</v>
@@ -35205,7 +35246,7 @@
         <v>84.8</v>
       </c>
       <c r="L33" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="M33">
         <v>179832</v>
@@ -35219,10 +35260,10 @@
         <v>736</v>
       </c>
       <c r="C34" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="D34" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="E34" t="s">
         <v>17</v>
@@ -35257,13 +35298,13 @@
         <v>26</v>
       </c>
       <c r="B35" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="C35" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="D35" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="E35" t="s">
         <v>45</v>
@@ -35298,13 +35339,13 @@
         <v>26</v>
       </c>
       <c r="B36" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="C36" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="D36" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="E36" t="s">
         <v>379</v>
@@ -35336,10 +35377,10 @@
         <v>93</v>
       </c>
       <c r="C37" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="D37" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="E37" t="s">
         <v>17</v>
@@ -35380,7 +35421,7 @@
         <v>497</v>
       </c>
       <c r="D38" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="E38" t="s">
         <v>17</v>
@@ -35404,7 +35445,7 @@
         <v>64.34</v>
       </c>
       <c r="L38" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="M38">
         <v>228275</v>
@@ -35418,10 +35459,10 @@
         <v>93</v>
       </c>
       <c r="C39" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="D39" t="s">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="E39" t="s">
         <v>17</v>
@@ -35459,10 +35500,10 @@
         <v>351</v>
       </c>
       <c r="C40" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="D40" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="E40" t="s">
         <v>17</v>
@@ -35503,7 +35544,7 @@
         <v>497</v>
       </c>
       <c r="D41" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="E41" t="s">
         <v>179</v>
@@ -35521,7 +35562,7 @@
         <v>70</v>
       </c>
       <c r="L41" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="M41">
         <v>0</v>
@@ -35535,10 +35576,10 @@
         <v>432</v>
       </c>
       <c r="C42" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="D42" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="E42" t="s">
         <v>17</v>
@@ -35562,7 +35603,7 @@
         <v>73.27</v>
       </c>
       <c r="L42" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="M42">
         <v>232260</v>
@@ -35576,10 +35617,10 @@
         <v>432</v>
       </c>
       <c r="C43" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="D43" t="s">
-        <v>1174</v>
+        <v>1176</v>
       </c>
       <c r="E43" t="s">
         <v>17</v>
@@ -35617,10 +35658,10 @@
         <v>93</v>
       </c>
       <c r="C44" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="D44" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="E44" t="s">
         <v>17</v>
@@ -35658,10 +35699,10 @@
         <v>70</v>
       </c>
       <c r="C45" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="D45" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="E45" t="s">
         <v>17</v>
@@ -35685,7 +35726,7 @@
         <v>97.78</v>
       </c>
       <c r="L45" t="s">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="M45">
         <v>180397</v>
@@ -35699,10 +35740,10 @@
         <v>736</v>
       </c>
       <c r="C46" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="D46" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="E46" t="s">
         <v>17</v>
@@ -35726,7 +35767,7 @@
         <v>101.3</v>
       </c>
       <c r="L46" t="s">
-        <v>1176</v>
+        <v>1178</v>
       </c>
       <c r="M46">
         <v>191701</v>
@@ -35740,10 +35781,10 @@
         <v>75</v>
       </c>
       <c r="C47" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="D47" t="s">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="E47" t="s">
         <v>17</v>
@@ -35767,7 +35808,7 @@
         <v>90.11</v>
       </c>
       <c r="L47" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="M47">
         <v>226529</v>
@@ -35781,10 +35822,10 @@
         <v>75</v>
       </c>
       <c r="C48" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="D48" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="E48" t="s">
         <v>17</v>
@@ -35822,10 +35863,10 @@
         <v>75</v>
       </c>
       <c r="C49" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="D49" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="E49" t="s">
         <v>17</v>
@@ -35863,10 +35904,10 @@
         <v>736</v>
       </c>
       <c r="C50" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="D50" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="E50" t="s">
         <v>17</v>
@@ -35904,10 +35945,10 @@
         <v>736</v>
       </c>
       <c r="C51" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="D51" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="E51" t="s">
         <v>17</v>
@@ -35931,7 +35972,7 @@
         <v>19.5</v>
       </c>
       <c r="L51" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="M51">
         <v>197295</v>
@@ -35942,13 +35983,13 @@
         <v>29</v>
       </c>
       <c r="B52" t="s">
-        <v>1178</v>
+        <v>1180</v>
       </c>
       <c r="C52" t="s">
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="D52" t="s">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="E52" t="s">
         <v>45</v>
@@ -35972,7 +36013,7 @@
         <v>41.65</v>
       </c>
       <c r="L52" t="s">
-        <v>1179</v>
+        <v>1181</v>
       </c>
       <c r="M52">
         <v>235041</v>
@@ -35983,13 +36024,13 @@
         <v>29</v>
       </c>
       <c r="B53" t="s">
-        <v>1178</v>
+        <v>1180</v>
       </c>
       <c r="C53" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="D53" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="E53" t="s">
         <v>379</v>
@@ -36007,7 +36048,7 @@
         <v>8.35</v>
       </c>
       <c r="L53" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="M53">
         <v>224007</v>
@@ -36021,10 +36062,10 @@
         <v>75</v>
       </c>
       <c r="C54" t="s">
-        <v>1160</v>
+        <v>1162</v>
       </c>
       <c r="D54" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="E54" t="s">
         <v>17</v>
@@ -36048,7 +36089,7 @@
         <v>39.229999999999997</v>
       </c>
       <c r="L54" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="M54">
         <v>56434</v>
@@ -36062,10 +36103,10 @@
         <v>93</v>
       </c>
       <c r="C55" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="D55" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="E55" t="s">
         <v>17</v>
@@ -36089,7 +36130,7 @@
         <v>487.46</v>
       </c>
       <c r="L55" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="M55">
         <v>994577</v>
@@ -36103,10 +36144,10 @@
         <v>93</v>
       </c>
       <c r="C56" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="D56" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="E56" t="s">
         <v>17</v>
@@ -36147,7 +36188,7 @@
         <v>497</v>
       </c>
       <c r="D57" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="E57" t="s">
         <v>179</v>
@@ -36165,7 +36206,7 @@
         <v>32.56</v>
       </c>
       <c r="L57" t="s">
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="M57">
         <v>0</v>
@@ -36179,10 +36220,10 @@
         <v>93</v>
       </c>
       <c r="C58" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="D58" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="E58" t="s">
         <v>17</v>
@@ -36206,7 +36247,7 @@
         <v>100.62</v>
       </c>
       <c r="L58" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="M58">
         <v>672482</v>
@@ -36220,10 +36261,10 @@
         <v>70</v>
       </c>
       <c r="C59" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="D59" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="E59" t="s">
         <v>17</v>
@@ -36247,7 +36288,7 @@
         <v>103.05</v>
       </c>
       <c r="L59" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="M59">
         <v>180920</v>
@@ -36261,10 +36302,10 @@
         <v>237</v>
       </c>
       <c r="C60" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="D60" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="E60" t="s">
         <v>17</v>
@@ -36288,7 +36329,7 @@
         <v>113.01</v>
       </c>
       <c r="L60" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="M60">
         <v>192968</v>
@@ -36302,10 +36343,10 @@
         <v>93</v>
       </c>
       <c r="C61" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="D61" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="E61" t="s">
         <v>17</v>
@@ -36329,7 +36370,7 @@
         <v>81.12</v>
       </c>
       <c r="L61" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="M61">
         <v>232772</v>
@@ -36346,7 +36387,7 @@
         <v>497</v>
       </c>
       <c r="D62" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="E62" t="s">
         <v>17</v>
@@ -36370,7 +36411,7 @@
         <v>94.58</v>
       </c>
       <c r="L62" t="s">
-        <v>1186</v>
+        <v>1188</v>
       </c>
       <c r="M62">
         <v>0</v>
@@ -36384,10 +36425,10 @@
         <v>224</v>
       </c>
       <c r="C63" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="D63" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="E63" t="s">
         <v>17</v>
@@ -36425,10 +36466,10 @@
         <v>432</v>
       </c>
       <c r="C64" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="D64" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="E64" t="s">
         <v>17</v>
@@ -36466,10 +36507,10 @@
         <v>70</v>
       </c>
       <c r="C65" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="D65" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="E65" t="s">
         <v>17</v>
@@ -36493,7 +36534,7 @@
         <v>110.64</v>
       </c>
       <c r="L65" t="s">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="M65">
         <v>181499</v>
@@ -36507,10 +36548,10 @@
         <v>385</v>
       </c>
       <c r="C66" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="D66" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="E66" t="s">
         <v>17</v>
@@ -36534,7 +36575,7 @@
         <v>510.26</v>
       </c>
       <c r="L66" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="M66">
         <v>995669</v>
@@ -36548,10 +36589,10 @@
         <v>75</v>
       </c>
       <c r="C67" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="D67" t="s">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="E67" t="s">
         <v>17</v>
@@ -36575,7 +36616,7 @@
         <v>87.06</v>
       </c>
       <c r="L67" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="M67">
         <v>226912</v>
@@ -36589,10 +36630,10 @@
         <v>75</v>
       </c>
       <c r="C68" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="D68" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="E68" t="s">
         <v>17</v>
@@ -36630,10 +36671,10 @@
         <v>70</v>
       </c>
       <c r="C69" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="D69" t="s">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="E69" t="s">
         <v>17</v>
@@ -36657,7 +36698,7 @@
         <v>72.180000000000007</v>
       </c>
       <c r="L69" t="s">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="M69">
         <v>306214</v>
@@ -36671,10 +36712,10 @@
         <v>375</v>
       </c>
       <c r="C70" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
       <c r="D70" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
       <c r="E70" t="s">
         <v>45</v>
@@ -36712,10 +36753,10 @@
         <v>93</v>
       </c>
       <c r="C71" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="D71" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="E71" t="s">
         <v>17</v>
@@ -36750,13 +36791,13 @@
         <v>69</v>
       </c>
       <c r="B72" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="C72" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="D72" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="E72" t="s">
         <v>17</v>
@@ -36780,7 +36821,7 @@
         <v>120.5</v>
       </c>
       <c r="L72" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="M72">
         <v>194507</v>
@@ -36794,10 +36835,10 @@
         <v>93</v>
       </c>
       <c r="C73" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="D73" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="E73" t="s">
         <v>17</v>
@@ -36821,7 +36862,7 @@
         <v>97.76</v>
       </c>
       <c r="L73" t="s">
-        <v>1190</v>
+        <v>1192</v>
       </c>
       <c r="M73">
         <v>672908</v>
@@ -36835,10 +36876,10 @@
         <v>93</v>
       </c>
       <c r="C74" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="D74" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="E74" t="s">
         <v>17</v>
@@ -36876,10 +36917,10 @@
         <v>93</v>
       </c>
       <c r="C75" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="D75" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="E75" t="s">
         <v>17</v>
@@ -36917,10 +36958,10 @@
         <v>75</v>
       </c>
       <c r="C76" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="D76" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="E76" t="s">
         <v>17</v>
@@ -36955,13 +36996,13 @@
         <v>53</v>
       </c>
       <c r="B77" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="C77" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="D77" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="E77" t="s">
         <v>45</v>
@@ -36996,13 +37037,13 @@
         <v>53</v>
       </c>
       <c r="B78" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="C78" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="D78" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="E78" t="s">
         <v>379</v>
@@ -37034,10 +37075,10 @@
         <v>93</v>
       </c>
       <c r="C79" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="D79" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="E79" t="s">
         <v>17</v>
@@ -37075,10 +37116,10 @@
         <v>93</v>
       </c>
       <c r="C80" t="s">
-        <v>1160</v>
+        <v>1162</v>
       </c>
       <c r="D80" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="E80" t="s">
         <v>17</v>
@@ -37102,7 +37143,7 @@
         <v>111.41</v>
       </c>
       <c r="L80" t="s">
-        <v>1191</v>
+        <v>1193</v>
       </c>
       <c r="M80">
         <v>57052</v>
@@ -37116,10 +37157,10 @@
         <v>70</v>
       </c>
       <c r="C81" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="D81" t="s">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="E81" t="s">
         <v>17</v>
@@ -37143,7 +37184,7 @@
         <v>114.84</v>
       </c>
       <c r="L81" t="s">
-        <v>1192</v>
+        <v>1194</v>
       </c>
       <c r="M81">
         <v>306887</v>
@@ -37157,10 +37198,10 @@
         <v>75</v>
       </c>
       <c r="C82" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="D82" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="E82" t="s">
         <v>17</v>
@@ -37198,10 +37239,10 @@
         <v>93</v>
       </c>
       <c r="C83" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="D83" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="E83" t="s">
         <v>17</v>
@@ -37239,10 +37280,10 @@
         <v>93</v>
       </c>
       <c r="C84" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="D84" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="E84" t="s">
         <v>17</v>
@@ -37280,10 +37321,10 @@
         <v>736</v>
       </c>
       <c r="C85" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="D85" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="E85" t="s">
         <v>17</v>
@@ -37324,7 +37365,7 @@
         <v>497</v>
       </c>
       <c r="D86" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="E86" t="s">
         <v>17</v>
@@ -37348,7 +37389,7 @@
         <v>81.69</v>
       </c>
       <c r="L86" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="M86">
         <v>0</v>
@@ -37362,10 +37403,10 @@
         <v>204</v>
       </c>
       <c r="C87" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="D87" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="E87" t="s">
         <v>17</v>
@@ -37389,7 +37430,7 @@
         <v>587.09</v>
       </c>
       <c r="L87" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="M87">
         <v>998017</v>
@@ -37403,10 +37444,10 @@
         <v>204</v>
       </c>
       <c r="C88" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="D88" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="E88" t="s">
         <v>194</v>
@@ -37424,7 +37465,7 @@
         <v>55.21</v>
       </c>
       <c r="L88" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="M88">
         <v>998017</v>
@@ -37438,10 +37479,10 @@
         <v>75</v>
       </c>
       <c r="C89" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="D89" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="E89" t="s">
         <v>17</v>
@@ -37479,10 +37520,10 @@
         <v>97</v>
       </c>
       <c r="C90" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
       <c r="D90" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
       <c r="E90" t="s">
         <v>45</v>
@@ -37520,10 +37561,10 @@
         <v>432</v>
       </c>
       <c r="C91" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
       <c r="D91" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
       <c r="E91" t="s">
         <v>45</v>
@@ -37547,7 +37588,7 @@
         <v>12.54</v>
       </c>
       <c r="L91" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="M91">
         <v>126841</v>
@@ -37561,10 +37602,10 @@
         <v>93</v>
       </c>
       <c r="C92" t="s">
-        <v>1160</v>
+        <v>1162</v>
       </c>
       <c r="D92" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="E92" t="s">
         <v>17</v>
@@ -37602,10 +37643,10 @@
         <v>93</v>
       </c>
       <c r="C93" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="D93" t="s">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="E93" t="s">
         <v>17</v>
@@ -37629,7 +37670,7 @@
         <v>99.24</v>
       </c>
       <c r="L93" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="M93">
         <v>84500</v>
@@ -37643,10 +37684,10 @@
         <v>93</v>
       </c>
       <c r="C94" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="D94" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="E94" t="s">
         <v>17</v>
@@ -37670,7 +37711,7 @@
         <v>34.53</v>
       </c>
       <c r="L94" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="M94">
         <v>412884</v>
@@ -37684,10 +37725,10 @@
         <v>93</v>
       </c>
       <c r="C95" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="D95" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="E95" t="s">
         <v>17</v>
@@ -37711,7 +37752,7 @@
         <v>69.63</v>
       </c>
       <c r="L95" t="s">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="M95">
         <v>235875</v>
@@ -37725,10 +37766,10 @@
         <v>93</v>
       </c>
       <c r="C96" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="D96" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="E96" t="s">
         <v>17</v>
@@ -37752,7 +37793,7 @@
         <v>110.02</v>
       </c>
       <c r="L96" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="M96">
         <v>362704</v>
@@ -37766,10 +37807,10 @@
         <v>70</v>
       </c>
       <c r="C97" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="D97" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="E97" t="s">
         <v>17</v>
@@ -37793,7 +37834,7 @@
         <v>123.34</v>
       </c>
       <c r="L97" t="s">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="M97">
         <v>182063</v>
@@ -37807,10 +37848,10 @@
         <v>736</v>
       </c>
       <c r="C98" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="D98" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="E98" t="s">
         <v>17</v>
@@ -37834,7 +37875,7 @@
         <v>113.99</v>
       </c>
       <c r="L98" t="s">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="M98">
         <v>198010</v>
@@ -37848,10 +37889,10 @@
         <v>75</v>
       </c>
       <c r="C99" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="D99" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="E99" t="s">
         <v>17</v>
@@ -37875,7 +37916,7 @@
         <v>54.3</v>
       </c>
       <c r="L99" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="M99">
         <v>0</v>
@@ -37889,10 +37930,10 @@
         <v>75</v>
       </c>
       <c r="C100" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="D100" t="s">
-        <v>1174</v>
+        <v>1176</v>
       </c>
       <c r="E100" t="s">
         <v>17</v>
@@ -37981,10 +38022,10 @@
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="D2" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="E2" t="s">
         <v>17</v>
@@ -38008,7 +38049,7 @@
         <v>61.07</v>
       </c>
       <c r="L2" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -38022,10 +38063,10 @@
         <v>93</v>
       </c>
       <c r="C3" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="D3" t="s">
-        <v>1206</v>
+        <v>1208</v>
       </c>
       <c r="E3" t="s">
         <v>17</v>
@@ -38063,10 +38104,10 @@
         <v>93</v>
       </c>
       <c r="C4" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="D4" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="E4" t="s">
         <v>17</v>
@@ -38090,7 +38131,7 @@
         <v>69.22</v>
       </c>
       <c r="L4" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="M4">
         <v>0</v>
@@ -38104,10 +38145,10 @@
         <v>93</v>
       </c>
       <c r="C5" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="D5" t="s">
-        <v>1206</v>
+        <v>1208</v>
       </c>
       <c r="E5" t="s">
         <v>17</v>
@@ -38145,10 +38186,10 @@
         <v>93</v>
       </c>
       <c r="C6" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="D6" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="E6" t="s">
         <v>17</v>
@@ -38172,7 +38213,7 @@
         <v>65.08</v>
       </c>
       <c r="L6" t="s">
-        <v>1186</v>
+        <v>1188</v>
       </c>
       <c r="M6">
         <v>0</v>
@@ -38186,10 +38227,10 @@
         <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>1208</v>
+        <v>1210</v>
       </c>
       <c r="D7" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="E7" t="s">
         <v>17</v>
@@ -38213,7 +38254,7 @@
         <v>78.930000000000007</v>
       </c>
       <c r="L7" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
       <c r="M7">
         <v>422600</v>
@@ -38227,10 +38268,10 @@
         <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>1208</v>
+        <v>1210</v>
       </c>
       <c r="D8" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="E8" t="s">
         <v>17</v>
@@ -38268,10 +38309,10 @@
         <v>93</v>
       </c>
       <c r="C9" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="D9" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="E9" t="s">
         <v>17</v>
@@ -38295,7 +38336,7 @@
         <v>60.42</v>
       </c>
       <c r="L9" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="M9">
         <v>0</v>
@@ -38309,10 +38350,10 @@
         <v>93</v>
       </c>
       <c r="C10" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="D10" t="s">
-        <v>1206</v>
+        <v>1208</v>
       </c>
       <c r="E10" t="s">
         <v>17</v>
@@ -38350,10 +38391,10 @@
         <v>93</v>
       </c>
       <c r="C11" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="D11" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="E11" t="s">
         <v>17</v>
@@ -38442,10 +38483,10 @@
         <v>415</v>
       </c>
       <c r="C2" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="D2" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="E2" t="s">
         <v>179</v>
@@ -38483,10 +38524,10 @@
         <v>432</v>
       </c>
       <c r="C3" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="D3" t="s">
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="E3" t="s">
         <v>240</v>
@@ -38510,7 +38551,7 @@
         <v>110.64</v>
       </c>
       <c r="L3" t="s">
-        <v>1215</v>
+        <v>1217</v>
       </c>
       <c r="M3">
         <v>0</v>
@@ -38524,10 +38565,10 @@
         <v>151</v>
       </c>
       <c r="C4" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="D4" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="E4" t="s">
         <v>17</v>
@@ -38551,7 +38592,7 @@
         <v>58.85</v>
       </c>
       <c r="L4" t="s">
-        <v>1218</v>
+        <v>1220</v>
       </c>
       <c r="M4">
         <v>349588</v>
@@ -38565,10 +38606,10 @@
         <v>97</v>
       </c>
       <c r="C5" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="D5" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="E5" t="s">
         <v>179</v>
@@ -38606,10 +38647,10 @@
         <v>97</v>
       </c>
       <c r="C6" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="D6" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="E6" t="s">
         <v>17</v>
@@ -38633,7 +38674,7 @@
         <v>79.989999999999995</v>
       </c>
       <c r="L6" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="M6">
         <v>326660</v>
@@ -38647,10 +38688,10 @@
         <v>442</v>
       </c>
       <c r="C7" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="D7" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
       <c r="E7" t="s">
         <v>17</v>
@@ -38674,7 +38715,7 @@
         <v>49.69</v>
       </c>
       <c r="L7" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="M7">
         <v>0</v>
@@ -38688,10 +38729,10 @@
         <v>442</v>
       </c>
       <c r="C8" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="D8" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
       <c r="E8" t="s">
         <v>17</v>
@@ -38715,7 +38756,7 @@
         <v>31.48</v>
       </c>
       <c r="L8" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="M8">
         <v>0</v>
@@ -38729,10 +38770,10 @@
         <v>93</v>
       </c>
       <c r="C9" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
       <c r="D9" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="E9" t="s">
         <v>17</v>
@@ -38770,10 +38811,10 @@
         <v>144</v>
       </c>
       <c r="C10" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="D10" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="E10" t="s">
         <v>17</v>
@@ -38797,7 +38838,7 @@
         <v>45.81</v>
       </c>
       <c r="L10" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="M10">
         <v>350060</v>
@@ -38811,10 +38852,10 @@
         <v>375</v>
       </c>
       <c r="C11" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
       <c r="D11" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="E11" t="s">
         <v>179</v>
@@ -38852,10 +38893,10 @@
         <v>97</v>
       </c>
       <c r="C12" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="D12" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="E12" t="s">
         <v>179</v>
@@ -38879,7 +38920,7 @@
         <v>147.28</v>
       </c>
       <c r="L12" t="s">
-        <v>1191</v>
+        <v>1193</v>
       </c>
       <c r="M12">
         <v>0</v>
@@ -38893,10 +38934,10 @@
         <v>202</v>
       </c>
       <c r="C13" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="D13" t="s">
-        <v>1230</v>
+        <v>1232</v>
       </c>
       <c r="E13" t="s">
         <v>17</v>
@@ -38934,10 +38975,10 @@
         <v>202</v>
       </c>
       <c r="C14" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="D14" t="s">
-        <v>1230</v>
+        <v>1232</v>
       </c>
       <c r="E14" t="s">
         <v>259</v>
@@ -38969,10 +39010,10 @@
         <v>392</v>
       </c>
       <c r="C15" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="D15" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="E15" t="s">
         <v>17</v>
@@ -38996,7 +39037,7 @@
         <v>63.52</v>
       </c>
       <c r="L15" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="M15">
         <v>0</v>
@@ -39010,10 +39051,10 @@
         <v>495</v>
       </c>
       <c r="C16" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="D16" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
       <c r="E16" t="s">
         <v>17</v>
@@ -39048,13 +39089,13 @@
         <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="C17" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="D17" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="E17" t="s">
         <v>17</v>
@@ -39092,10 +39133,10 @@
         <v>432</v>
       </c>
       <c r="C18" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="D18" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="E18" t="s">
         <v>17</v>
@@ -39133,10 +39174,10 @@
         <v>93</v>
       </c>
       <c r="C19" t="s">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="D19" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="E19" t="s">
         <v>45</v>
@@ -39174,10 +39215,10 @@
         <v>75</v>
       </c>
       <c r="C20" t="s">
-        <v>1239</v>
+        <v>1241</v>
       </c>
       <c r="D20" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="E20" t="s">
         <v>17</v>
@@ -39215,10 +39256,10 @@
         <v>442</v>
       </c>
       <c r="C21" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="D21" t="s">
-        <v>1230</v>
+        <v>1232</v>
       </c>
       <c r="E21" t="s">
         <v>17</v>
@@ -39242,7 +39283,7 @@
         <v>120.35</v>
       </c>
       <c r="L21" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="M21">
         <v>0</v>
@@ -39256,10 +39297,10 @@
         <v>202</v>
       </c>
       <c r="C22" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="D22" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="E22" t="s">
         <v>17</v>
@@ -39297,10 +39338,10 @@
         <v>754</v>
       </c>
       <c r="C23" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="D23" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="E23" t="s">
         <v>17</v>
@@ -39324,7 +39365,7 @@
         <v>69.23</v>
       </c>
       <c r="L23" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="M23">
         <v>0</v>
@@ -39338,10 +39379,10 @@
         <v>93</v>
       </c>
       <c r="C24" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
       <c r="D24" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="E24" t="s">
         <v>17</v>
@@ -39365,7 +39406,7 @@
         <v>49.05</v>
       </c>
       <c r="L24" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
       <c r="M24">
         <v>291662</v>
@@ -39379,10 +39420,10 @@
         <v>413</v>
       </c>
       <c r="C25" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="D25" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="E25" t="s">
         <v>17</v>
@@ -39420,10 +39461,10 @@
         <v>375</v>
       </c>
       <c r="C26" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="D26" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="E26" t="s">
         <v>179</v>
@@ -39461,10 +39502,10 @@
         <v>97</v>
       </c>
       <c r="C27" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
       <c r="D27" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="E27" t="s">
         <v>240</v>
@@ -39502,10 +39543,10 @@
         <v>97</v>
       </c>
       <c r="C28" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="D28" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="E28" t="s">
         <v>179</v>
@@ -39529,7 +39570,7 @@
         <v>63.89</v>
       </c>
       <c r="L28" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="M28">
         <v>0</v>
@@ -39543,10 +39584,10 @@
         <v>442</v>
       </c>
       <c r="C29" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="D29" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
       <c r="E29" t="s">
         <v>17</v>
@@ -39570,7 +39611,7 @@
         <v>65.28</v>
       </c>
       <c r="L29" t="s">
-        <v>1247</v>
+        <v>1249</v>
       </c>
       <c r="M29">
         <v>0</v>
@@ -39584,10 +39625,10 @@
         <v>442</v>
       </c>
       <c r="C30" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="D30" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
       <c r="E30" t="s">
         <v>17</v>
@@ -39625,10 +39666,10 @@
         <v>93</v>
       </c>
       <c r="C31" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="D31" t="s">
-        <v>1249</v>
+        <v>1251</v>
       </c>
       <c r="E31" t="s">
         <v>17</v>
@@ -39652,7 +39693,7 @@
         <v>95.34</v>
       </c>
       <c r="L31" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
       <c r="M31">
         <v>0</v>
@@ -39666,10 +39707,10 @@
         <v>93</v>
       </c>
       <c r="C32" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
       <c r="D32" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="E32" t="s">
         <v>179</v>
@@ -39693,7 +39734,7 @@
         <v>105.39</v>
       </c>
       <c r="L32" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
       <c r="M32">
         <v>0</v>
@@ -39707,10 +39748,10 @@
         <v>375</v>
       </c>
       <c r="C33" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="D33" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="E33" t="s">
         <v>17</v>
@@ -39748,10 +39789,10 @@
         <v>375</v>
       </c>
       <c r="C34" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
       <c r="D34" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="E34" t="s">
         <v>179</v>
@@ -39775,7 +39816,7 @@
         <v>112.34</v>
       </c>
       <c r="L34" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="M34">
         <v>0</v>
@@ -39789,10 +39830,10 @@
         <v>415</v>
       </c>
       <c r="C35" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="D35" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="E35" t="s">
         <v>179</v>
@@ -39816,7 +39857,7 @@
         <v>76.069999999999993</v>
       </c>
       <c r="L35" t="s">
-        <v>1254</v>
+        <v>1256</v>
       </c>
       <c r="M35">
         <v>0</v>
@@ -39830,10 +39871,10 @@
         <v>413</v>
       </c>
       <c r="C36" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="D36" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="E36" t="s">
         <v>17</v>
@@ -39857,7 +39898,7 @@
         <v>68.569999999999993</v>
       </c>
       <c r="L36" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="M36">
         <v>0</v>
@@ -39871,10 +39912,10 @@
         <v>97</v>
       </c>
       <c r="C37" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="D37" t="s">
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="E37" t="s">
         <v>240</v>
@@ -39912,10 +39953,10 @@
         <v>202</v>
       </c>
       <c r="C38" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="D38" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="E38" t="s">
         <v>17</v>
@@ -39939,7 +39980,7 @@
         <v>46.47</v>
       </c>
       <c r="L38" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
       <c r="M38">
         <v>371889</v>
@@ -39953,10 +39994,10 @@
         <v>408</v>
       </c>
       <c r="C39" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="D39" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="E39" t="s">
         <v>17</v>
@@ -39980,7 +40021,7 @@
         <v>66.89</v>
       </c>
       <c r="L39" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="M39">
         <v>352194</v>
@@ -39994,10 +40035,10 @@
         <v>294</v>
       </c>
       <c r="C40" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="D40" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="E40" t="s">
         <v>17</v>
@@ -40021,7 +40062,7 @@
         <v>35.93</v>
       </c>
       <c r="L40" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="M40">
         <v>352353</v>
@@ -40035,10 +40076,10 @@
         <v>97</v>
       </c>
       <c r="C41" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="D41" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="E41" t="s">
         <v>179</v>
@@ -40076,10 +40117,10 @@
         <v>380</v>
       </c>
       <c r="C42" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
       <c r="D42" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
       <c r="E42" t="s">
         <v>17</v>
@@ -40103,7 +40144,7 @@
         <v>92.75</v>
       </c>
       <c r="L42" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="M42">
         <v>300087</v>
@@ -40117,10 +40158,10 @@
         <v>410</v>
       </c>
       <c r="C43" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="D43" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="E43" t="s">
         <v>17</v>
@@ -40144,7 +40185,7 @@
         <v>68.97</v>
       </c>
       <c r="L43" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="M43">
         <v>0</v>
@@ -40158,10 +40199,10 @@
         <v>294</v>
       </c>
       <c r="C44" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="D44" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
       <c r="E44" t="s">
         <v>17</v>
@@ -40185,7 +40226,7 @@
         <v>47.66</v>
       </c>
       <c r="L44" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
       <c r="M44">
         <v>389572</v>
@@ -40199,10 +40240,10 @@
         <v>442</v>
       </c>
       <c r="C45" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="D45" t="s">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="E45" t="s">
         <v>17</v>
@@ -40226,7 +40267,7 @@
         <v>87.53</v>
       </c>
       <c r="L45" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
       <c r="M45">
         <v>0</v>
@@ -40237,13 +40278,13 @@
         <v>26</v>
       </c>
       <c r="B46" t="s">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="C46" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="D46" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="E46" t="s">
         <v>17</v>
@@ -40267,7 +40308,7 @@
         <v>59.27</v>
       </c>
       <c r="L46" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="M46">
         <v>0</v>
@@ -40281,10 +40322,10 @@
         <v>202</v>
       </c>
       <c r="C47" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="D47" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="E47" t="s">
         <v>17</v>
@@ -40308,7 +40349,7 @@
         <v>66.44</v>
       </c>
       <c r="L47" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="M47">
         <v>0</v>
@@ -40322,10 +40363,10 @@
         <v>432</v>
       </c>
       <c r="C48" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="D48" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="E48" t="s">
         <v>17</v>
@@ -40363,10 +40404,10 @@
         <v>93</v>
       </c>
       <c r="C49" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="D49" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="E49" t="s">
         <v>17</v>
@@ -40404,10 +40445,10 @@
         <v>93</v>
       </c>
       <c r="C50" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
       <c r="D50" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="E50" t="s">
         <v>17</v>
@@ -40445,10 +40486,10 @@
         <v>410</v>
       </c>
       <c r="C51" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="D51" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="E51" t="s">
         <v>17</v>
@@ -40472,7 +40513,7 @@
         <v>131.66</v>
       </c>
       <c r="L51" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="M51">
         <v>0</v>
@@ -40486,10 +40527,10 @@
         <v>294</v>
       </c>
       <c r="C52" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="D52" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="E52" t="s">
         <v>17</v>
@@ -40513,7 +40554,7 @@
         <v>43.55</v>
       </c>
       <c r="L52" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="M52">
         <v>0</v>
@@ -40527,10 +40568,10 @@
         <v>375</v>
       </c>
       <c r="C53" t="s">
-        <v>1269</v>
+        <v>1271</v>
       </c>
       <c r="D53" t="s">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="E53" t="s">
         <v>179</v>
@@ -40554,7 +40595,7 @@
         <v>60.9</v>
       </c>
       <c r="L53" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="M53">
         <v>292487</v>
@@ -40568,10 +40609,10 @@
         <v>375</v>
       </c>
       <c r="C54" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
       <c r="D54" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="E54" t="s">
         <v>179</v>
@@ -40609,10 +40650,10 @@
         <v>93</v>
       </c>
       <c r="C55" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="D55" t="s">
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="E55" t="s">
         <v>240</v>
@@ -40650,10 +40691,10 @@
         <v>93</v>
       </c>
       <c r="C56" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="D56" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="E56" t="s">
         <v>179</v>
@@ -40691,10 +40732,10 @@
         <v>151</v>
       </c>
       <c r="C57" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="D57" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="E57" t="s">
         <v>17</v>
@@ -40718,7 +40759,7 @@
         <v>53.4</v>
       </c>
       <c r="L57" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="M57">
         <v>0</v>
@@ -40732,10 +40773,10 @@
         <v>97</v>
       </c>
       <c r="C58" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="D58" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="E58" t="s">
         <v>179</v>
@@ -40759,7 +40800,7 @@
         <v>108.82</v>
       </c>
       <c r="L58" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
       <c r="M58">
         <v>0</v>
@@ -40773,10 +40814,10 @@
         <v>93</v>
       </c>
       <c r="C59" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="D59" t="s">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="E59" t="s">
         <v>17</v>
@@ -40800,7 +40841,7 @@
         <v>142.71</v>
       </c>
       <c r="L59" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="M59">
         <v>0</v>
@@ -40814,10 +40855,10 @@
         <v>93</v>
       </c>
       <c r="C60" t="s">
-        <v>1239</v>
+        <v>1241</v>
       </c>
       <c r="D60" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="E60" t="s">
         <v>179</v>
@@ -40841,7 +40882,7 @@
         <v>86.48</v>
       </c>
       <c r="L60" t="s">
-        <v>1275</v>
+        <v>1277</v>
       </c>
       <c r="M60">
         <v>0</v>
@@ -40855,10 +40896,10 @@
         <v>75</v>
       </c>
       <c r="C61" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
       <c r="D61" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="E61" t="s">
         <v>17</v>
@@ -40896,10 +40937,10 @@
         <v>202</v>
       </c>
       <c r="C62" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="D62" t="s">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="E62" t="s">
         <v>17</v>
@@ -40923,7 +40964,7 @@
         <v>87.05</v>
       </c>
       <c r="L62" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="M62">
         <v>0</v>
@@ -40937,10 +40978,10 @@
         <v>97</v>
       </c>
       <c r="C63" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
       <c r="D63" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="E63" t="s">
         <v>240</v>
@@ -40964,7 +41005,7 @@
         <v>155</v>
       </c>
       <c r="L63" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="M63">
         <v>0</v>
@@ -40978,10 +41019,10 @@
         <v>442</v>
       </c>
       <c r="C64" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
       <c r="D64" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="E64" t="s">
         <v>45</v>
@@ -41016,13 +41057,13 @@
         <v>38</v>
       </c>
       <c r="B65" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="C65" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="D65" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="E65" t="s">
         <v>17</v>
@@ -41060,10 +41101,10 @@
         <v>432</v>
       </c>
       <c r="C66" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="D66" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="E66" t="s">
         <v>179</v>
@@ -41087,7 +41128,7 @@
         <v>58.54</v>
       </c>
       <c r="L66" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="M66">
         <v>0</v>
@@ -41101,10 +41142,10 @@
         <v>93</v>
       </c>
       <c r="C67" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="D67" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="E67" t="s">
         <v>17</v>
@@ -41128,7 +41169,7 @@
         <v>47.39</v>
       </c>
       <c r="L67" t="s">
-        <v>1277</v>
+        <v>1279</v>
       </c>
       <c r="M67">
         <v>0</v>
@@ -41142,10 +41183,10 @@
         <v>93</v>
       </c>
       <c r="C68" t="s">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="D68" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="E68" t="s">
         <v>45</v>
@@ -41183,10 +41224,10 @@
         <v>93</v>
       </c>
       <c r="C69" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
       <c r="D69" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="E69" t="s">
         <v>17</v>
@@ -41224,10 +41265,10 @@
         <v>97</v>
       </c>
       <c r="C70" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="D70" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="E70" t="s">
         <v>17</v>
@@ -41265,10 +41306,10 @@
         <v>97</v>
       </c>
       <c r="C71" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
       <c r="D71" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="E71" t="s">
         <v>240</v>
@@ -41292,7 +41333,7 @@
         <v>139.99</v>
       </c>
       <c r="L71" t="s">
-        <v>1278</v>
+        <v>1280</v>
       </c>
       <c r="M71">
         <v>0</v>
@@ -41306,10 +41347,10 @@
         <v>442</v>
       </c>
       <c r="C72" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="D72" t="s">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="E72" t="s">
         <v>17</v>
@@ -41347,10 +41388,10 @@
         <v>442</v>
       </c>
       <c r="C73" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="D73" t="s">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="E73" t="s">
         <v>194</v>
@@ -41379,13 +41420,13 @@
         <v>42</v>
       </c>
       <c r="B74" t="s">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="C74" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="D74" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="E74" t="s">
         <v>17</v>
@@ -41423,10 +41464,10 @@
         <v>202</v>
       </c>
       <c r="C75" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="D75" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="E75" t="s">
         <v>17</v>
@@ -41450,7 +41491,7 @@
         <v>53.4</v>
       </c>
       <c r="L75" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="M75">
         <v>0</v>
@@ -41464,10 +41505,10 @@
         <v>432</v>
       </c>
       <c r="C76" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="D76" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="E76" t="s">
         <v>17</v>
@@ -41505,10 +41546,10 @@
         <v>97</v>
       </c>
       <c r="C77" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="D77" t="s">
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="E77" t="s">
         <v>240</v>
@@ -41532,7 +41573,7 @@
         <v>118.17</v>
       </c>
       <c r="L77" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
       <c r="M77">
         <v>0</v>
@@ -41546,10 +41587,10 @@
         <v>97</v>
       </c>
       <c r="C78" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="D78" t="s">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="E78" t="s">
         <v>45</v>
@@ -41573,7 +41614,7 @@
         <v>53.62</v>
       </c>
       <c r="L78" t="s">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="M78">
         <v>11945</v>
@@ -41587,10 +41628,10 @@
         <v>375</v>
       </c>
       <c r="C79" t="s">
-        <v>1269</v>
+        <v>1271</v>
       </c>
       <c r="D79" t="s">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="E79" t="s">
         <v>179</v>
@@ -41628,10 +41669,10 @@
         <v>93</v>
       </c>
       <c r="C80" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
       <c r="D80" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="E80" t="s">
         <v>17</v>
@@ -41655,7 +41696,7 @@
         <v>33.1</v>
       </c>
       <c r="L80" t="s">
-        <v>1285</v>
+        <v>1287</v>
       </c>
       <c r="M80">
         <v>293186</v>
@@ -41669,10 +41710,10 @@
         <v>375</v>
       </c>
       <c r="C81" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
       <c r="D81" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="E81" t="s">
         <v>179</v>
@@ -41696,7 +41737,7 @@
         <v>148.44999999999999</v>
       </c>
       <c r="L81" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="M81">
         <v>0</v>
@@ -41710,10 +41751,10 @@
         <v>97</v>
       </c>
       <c r="C82" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="D82" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="E82" t="s">
         <v>179</v>
@@ -41751,10 +41792,10 @@
         <v>442</v>
       </c>
       <c r="C83" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="D83" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
       <c r="E83" t="s">
         <v>17</v>
@@ -41778,7 +41819,7 @@
         <v>51.21</v>
       </c>
       <c r="L83" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="M83">
         <v>390823</v>
@@ -41792,10 +41833,10 @@
         <v>442</v>
       </c>
       <c r="C84" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="D84" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
       <c r="E84" t="s">
         <v>17</v>
@@ -41833,10 +41874,10 @@
         <v>93</v>
       </c>
       <c r="C85" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
       <c r="D85" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="E85" t="s">
         <v>17</v>
@@ -41860,7 +41901,7 @@
         <v>46.13</v>
       </c>
       <c r="L85" t="s">
-        <v>1288</v>
+        <v>1290</v>
       </c>
       <c r="M85">
         <v>293478</v>
@@ -41874,10 +41915,10 @@
         <v>736</v>
       </c>
       <c r="C86" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="D86" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="E86" t="s">
         <v>17</v>
@@ -41901,7 +41942,7 @@
         <v>62.32</v>
       </c>
       <c r="L86" t="s">
-        <v>1289</v>
+        <v>1291</v>
       </c>
       <c r="M86">
         <v>0</v>
@@ -41915,10 +41956,10 @@
         <v>75</v>
       </c>
       <c r="C87" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="D87" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="E87" t="s">
         <v>179</v>
@@ -41942,7 +41983,7 @@
         <v>82.73</v>
       </c>
       <c r="L87" t="s">
-        <v>1290</v>
+        <v>1292</v>
       </c>
       <c r="M87">
         <v>360108</v>
@@ -41956,10 +41997,10 @@
         <v>413</v>
       </c>
       <c r="C88" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="D88" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="E88" t="s">
         <v>17</v>
@@ -41997,10 +42038,10 @@
         <v>202</v>
       </c>
       <c r="C89" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="D89" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="E89" t="s">
         <v>17</v>
@@ -42038,10 +42079,10 @@
         <v>432</v>
       </c>
       <c r="C90" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="D90" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="E90" t="s">
         <v>17</v>
@@ -42065,7 +42106,7 @@
         <v>79.069999999999993</v>
       </c>
       <c r="L90" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="M90">
         <v>329125</v>
@@ -42079,10 +42120,10 @@
         <v>97</v>
       </c>
       <c r="C91" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="D91" t="s">
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="E91" t="s">
         <v>240</v>
@@ -42117,13 +42158,13 @@
         <v>69</v>
       </c>
       <c r="B92" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C92" t="s">
+        <v>1233</v>
+      </c>
+      <c r="D92" t="s">
         <v>1234</v>
-      </c>
-      <c r="C92" t="s">
-        <v>1231</v>
-      </c>
-      <c r="D92" t="s">
-        <v>1232</v>
       </c>
       <c r="E92" t="s">
         <v>17</v>
@@ -42161,10 +42202,10 @@
         <v>93</v>
       </c>
       <c r="C93" t="s">
-        <v>1239</v>
+        <v>1241</v>
       </c>
       <c r="D93" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="E93" t="s">
         <v>17</v>
@@ -42202,10 +42243,10 @@
         <v>380</v>
       </c>
       <c r="C94" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
       <c r="D94" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
       <c r="E94" t="s">
         <v>17</v>
@@ -42229,7 +42270,7 @@
         <v>95.01</v>
       </c>
       <c r="L94" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="M94">
         <v>300680</v>
@@ -42243,10 +42284,10 @@
         <v>380</v>
       </c>
       <c r="C95" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
       <c r="D95" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="E95" t="s">
         <v>179</v>
@@ -42270,7 +42311,7 @@
         <v>93.89</v>
       </c>
       <c r="L95" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="M95">
         <v>0</v>
@@ -42284,10 +42325,10 @@
         <v>290</v>
       </c>
       <c r="C96" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="D96" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="E96" t="s">
         <v>17</v>
@@ -42325,10 +42366,10 @@
         <v>442</v>
       </c>
       <c r="C97" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="D97" t="s">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="E97" t="s">
         <v>17</v>
@@ -42366,10 +42407,10 @@
         <v>442</v>
       </c>
       <c r="C98" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="D98" t="s">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="E98" t="s">
         <v>194</v>
@@ -42398,13 +42439,13 @@
         <v>53</v>
       </c>
       <c r="B99" t="s">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="C99" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="D99" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="E99" t="s">
         <v>17</v>
@@ -42428,7 +42469,7 @@
         <v>68.88</v>
       </c>
       <c r="L99" t="s">
-        <v>1289</v>
+        <v>1291</v>
       </c>
       <c r="M99">
         <v>357137</v>
@@ -42442,10 +42483,10 @@
         <v>202</v>
       </c>
       <c r="C100" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="D100" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="E100" t="s">
         <v>17</v>
@@ -42483,10 +42524,10 @@
         <v>93</v>
       </c>
       <c r="C101" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
       <c r="D101" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="E101" t="s">
         <v>17</v>
@@ -42524,10 +42565,10 @@
         <v>97</v>
       </c>
       <c r="C102" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="D102" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="E102" t="s">
         <v>179</v>
@@ -42565,10 +42606,10 @@
         <v>432</v>
       </c>
       <c r="C103" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="D103" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="E103" t="s">
         <v>17</v>
@@ -42592,7 +42633,7 @@
         <v>91</v>
       </c>
       <c r="L103" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="M103">
         <v>329590</v>
@@ -42606,10 +42647,10 @@
         <v>93</v>
       </c>
       <c r="C104" t="s">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="D104" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="E104" t="s">
         <v>45</v>
@@ -42633,7 +42674,7 @@
         <v>36.840000000000003</v>
       </c>
       <c r="L104" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="M104">
         <v>0</v>
@@ -42647,10 +42688,10 @@
         <v>442</v>
       </c>
       <c r="C105" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="D105" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="E105" t="s">
         <v>17</v>
@@ -42674,7 +42715,7 @@
         <v>56.82</v>
       </c>
       <c r="L105" t="s">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="M105">
         <v>0</v>
@@ -42688,10 +42729,10 @@
         <v>93</v>
       </c>
       <c r="C106" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="D106" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
       <c r="E106" t="s">
         <v>17</v>
@@ -42715,7 +42756,7 @@
         <v>37.770000000000003</v>
       </c>
       <c r="L106" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="M106">
         <v>0</v>
@@ -42729,10 +42770,10 @@
         <v>144</v>
       </c>
       <c r="C107" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="D107" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
       <c r="E107" t="s">
         <v>17</v>
@@ -42770,10 +42811,10 @@
         <v>375</v>
       </c>
       <c r="C108" t="s">
-        <v>1295</v>
+        <v>1297</v>
       </c>
       <c r="D108" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="E108" t="s">
         <v>17</v>
@@ -42811,10 +42852,10 @@
         <v>375</v>
       </c>
       <c r="C109" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
       <c r="D109" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="E109" t="s">
         <v>179</v>
@@ -42838,7 +42879,7 @@
         <v>141.1</v>
       </c>
       <c r="L109" t="s">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="M109">
         <v>0</v>
@@ -42852,10 +42893,10 @@
         <v>392</v>
       </c>
       <c r="C110" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="D110" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="E110" t="s">
         <v>17</v>
@@ -42893,10 +42934,10 @@
         <v>202</v>
       </c>
       <c r="C111" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="D111" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="E111" t="s">
         <v>17</v>
@@ -42920,7 +42961,7 @@
         <v>81.260000000000005</v>
       </c>
       <c r="L111" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="M111">
         <v>0</v>
@@ -42985,10 +43026,10 @@
         <v>392</v>
       </c>
       <c r="C2" t="s">
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="D2" t="s">
-        <v>1299</v>
+        <v>1301</v>
       </c>
       <c r="E2" t="s">
         <v>45</v>
@@ -43012,7 +43053,7 @@
         <v>38.53</v>
       </c>
       <c r="L2" t="s">
-        <v>1300</v>
+        <v>1302</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -43026,10 +43067,10 @@
         <v>93</v>
       </c>
       <c r="C3" t="s">
-        <v>1301</v>
+        <v>1303</v>
       </c>
       <c r="D3" t="s">
-        <v>1302</v>
+        <v>1304</v>
       </c>
       <c r="E3" t="s">
         <v>45</v>
@@ -43053,7 +43094,7 @@
         <v>56.73</v>
       </c>
       <c r="L3" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="M3">
         <v>0</v>
@@ -43067,10 +43108,10 @@
         <v>375</v>
       </c>
       <c r="C4" t="s">
-        <v>1303</v>
+        <v>1305</v>
       </c>
       <c r="D4" t="s">
-        <v>1304</v>
+        <v>1306</v>
       </c>
       <c r="E4" t="s">
         <v>45</v>
@@ -43094,7 +43135,7 @@
         <v>52.71</v>
       </c>
       <c r="L4" t="s">
-        <v>1305</v>
+        <v>1307</v>
       </c>
       <c r="M4">
         <v>0</v>
@@ -43107,7 +43148,7 @@
 
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2B00-000000000000}">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -43159,10 +43200,10 @@
         <v>166</v>
       </c>
       <c r="C2" t="s">
-        <v>1306</v>
+        <v>1308</v>
       </c>
       <c r="D2" t="s">
-        <v>1307</v>
+        <v>1309</v>
       </c>
       <c r="E2" t="s">
         <v>17</v>
@@ -43180,7 +43221,7 @@
         <v>115.93</v>
       </c>
       <c r="L2" t="s">
-        <v>1308</v>
+        <v>1310</v>
       </c>
       <c r="M2">
         <v>230400</v>
@@ -43191,13 +43232,13 @@
         <v>84</v>
       </c>
       <c r="B3" t="s">
+        <v>1311</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1308</v>
+      </c>
+      <c r="D3" t="s">
         <v>1309</v>
-      </c>
-      <c r="C3" t="s">
-        <v>1306</v>
-      </c>
-      <c r="D3" t="s">
-        <v>1307</v>
       </c>
       <c r="E3" t="s">
         <v>17</v>
@@ -43223,106 +43264,71 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="B4" t="s">
-        <v>375</v>
+        <v>1312</v>
       </c>
       <c r="C4" t="s">
-        <v>411</v>
+        <v>1308</v>
       </c>
       <c r="D4" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E4" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="F4">
-        <v>26.431999999999899</v>
+        <v>56.378999999999898</v>
       </c>
       <c r="G4" t="s">
         <v>18</v>
       </c>
       <c r="J4">
-        <v>1.46</v>
+        <v>1.61</v>
       </c>
       <c r="K4">
-        <v>38.590000000000003</v>
+        <v>90.77</v>
       </c>
       <c r="L4" t="s">
-        <v>1311</v>
+        <v>1313</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>231530</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="B5" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="C5" t="s">
-        <v>1306</v>
+        <v>1308</v>
       </c>
       <c r="D5" t="s">
-        <v>1307</v>
+        <v>1309</v>
       </c>
       <c r="E5" t="s">
         <v>17</v>
       </c>
       <c r="F5">
-        <v>56.378999999999898</v>
+        <v>55.5489999999999</v>
       </c>
       <c r="G5" t="s">
         <v>18</v>
       </c>
       <c r="J5">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="K5">
-        <v>90.77</v>
+        <v>89.99</v>
       </c>
       <c r="L5" t="s">
-        <v>1313</v>
+        <v>1108</v>
       </c>
       <c r="M5">
-        <v>231530</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>53</v>
-      </c>
-      <c r="B6" t="s">
-        <v>1309</v>
-      </c>
-      <c r="C6" t="s">
-        <v>1306</v>
-      </c>
-      <c r="D6" t="s">
-        <v>1307</v>
-      </c>
-      <c r="E6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6">
-        <v>55.5489999999999</v>
-      </c>
-      <c r="G6" t="s">
-        <v>18</v>
-      </c>
-      <c r="J6">
-        <v>1.62</v>
-      </c>
-      <c r="K6">
-        <v>89.99</v>
-      </c>
-      <c r="L6" t="s">
-        <v>1106</v>
-      </c>
-      <c r="M6">
         <v>232010</v>
       </c>
     </row>
@@ -43335,9 +43341,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:M24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
